--- a/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B07_Normal_1.xlsx
+++ b/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B07_Normal_1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J244"/>
+  <dimension ref="A1:K244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Segment_ID</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Area</t>
         </is>
       </c>
@@ -515,6 +520,9 @@
         </is>
       </c>
       <c r="J2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K2" t="n">
         <v>24.44938674448072</v>
       </c>
     </row>
@@ -553,6 +561,9 @@
         </is>
       </c>
       <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -591,6 +602,9 @@
         </is>
       </c>
       <c r="J4" t="n">
+        <v>5</v>
+      </c>
+      <c r="K4" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -629,6 +643,9 @@
         </is>
       </c>
       <c r="J5" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" t="n">
         <v>23.09469567725773</v>
       </c>
     </row>
@@ -667,6 +684,9 @@
         </is>
       </c>
       <c r="J6" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" t="n">
         <v>16.22537890841612</v>
       </c>
     </row>
@@ -705,6 +725,9 @@
         </is>
       </c>
       <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
         <v>15.92519383307983</v>
       </c>
     </row>
@@ -743,6 +766,9 @@
         </is>
       </c>
       <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="n">
         <v>15.55123726155539</v>
       </c>
     </row>
@@ -781,6 +807,9 @@
         </is>
       </c>
       <c r="J9" t="n">
+        <v>5</v>
+      </c>
+      <c r="K9" t="n">
         <v>15.50392193361757</v>
       </c>
     </row>
@@ -819,6 +848,9 @@
         </is>
       </c>
       <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
         <v>15.43409332138252</v>
       </c>
     </row>
@@ -857,6 +889,9 @@
         </is>
       </c>
       <c r="J11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K11" t="n">
         <v>15.43409332138252</v>
       </c>
     </row>
@@ -895,6 +930,9 @@
         </is>
       </c>
       <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
         <v>14.91383648998964</v>
       </c>
     </row>
@@ -933,6 +971,9 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" t="n">
         <v>14.91383648998964</v>
       </c>
     </row>
@@ -971,6 +1012,9 @@
         </is>
       </c>
       <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
         <v>13.96252814601202</v>
       </c>
     </row>
@@ -1009,6 +1053,9 @@
         </is>
       </c>
       <c r="J15" t="n">
+        <v>5</v>
+      </c>
+      <c r="K15" t="n">
         <v>12.8845474029381</v>
       </c>
     </row>
@@ -1047,6 +1094,9 @@
         </is>
       </c>
       <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
         <v>12.56557511094277</v>
       </c>
     </row>
@@ -1085,6 +1135,9 @@
         </is>
       </c>
       <c r="J17" t="n">
+        <v>5</v>
+      </c>
+      <c r="K17" t="n">
         <v>12.56557511094277</v>
       </c>
     </row>
@@ -1123,6 +1176,9 @@
         </is>
       </c>
       <c r="J18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K18" t="n">
         <v>12.42650727241244</v>
       </c>
     </row>
@@ -1161,6 +1217,9 @@
         </is>
       </c>
       <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
         <v>12.61222121789064</v>
       </c>
     </row>
@@ -1199,6 +1258,9 @@
         </is>
       </c>
       <c r="J20" t="n">
+        <v>5</v>
+      </c>
+      <c r="K20" t="n">
         <v>12.6149723565889</v>
       </c>
     </row>
@@ -1237,6 +1299,9 @@
         </is>
       </c>
       <c r="J21" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" t="n">
         <v>12.6149723565889</v>
       </c>
     </row>
@@ -1275,6 +1340,9 @@
         </is>
       </c>
       <c r="J22" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" t="n">
         <v>12.88726856229838</v>
       </c>
     </row>
@@ -1313,6 +1381,9 @@
         </is>
       </c>
       <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
         <v>13.08268414389388</v>
       </c>
     </row>
@@ -1351,6 +1422,9 @@
         </is>
       </c>
       <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
         <v>13.11655963642752</v>
       </c>
     </row>
@@ -1389,6 +1463,9 @@
         </is>
       </c>
       <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
         <v>13.06477406907523</v>
       </c>
     </row>
@@ -1427,6 +1504,9 @@
         </is>
       </c>
       <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
         <v>13.00822550737505</v>
       </c>
     </row>
@@ -1465,6 +1545,9 @@
         </is>
       </c>
       <c r="J27" t="n">
+        <v>5</v>
+      </c>
+      <c r="K27" t="n">
         <v>13.00822550737505</v>
       </c>
     </row>
@@ -1503,6 +1586,9 @@
         </is>
       </c>
       <c r="J28" t="n">
+        <v>5</v>
+      </c>
+      <c r="K28" t="n">
         <v>12.82946633796654</v>
       </c>
     </row>
@@ -1541,6 +1627,9 @@
         </is>
       </c>
       <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
         <v>12.72199060197538</v>
       </c>
     </row>
@@ -1579,6 +1668,9 @@
         </is>
       </c>
       <c r="J30" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" t="n">
         <v>12.76786570293602</v>
       </c>
     </row>
@@ -1617,6 +1709,9 @@
         </is>
       </c>
       <c r="J31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" t="n">
         <v>12.94918332241907</v>
       </c>
     </row>
@@ -1655,6 +1750,9 @@
         </is>
       </c>
       <c r="J32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K32" t="n">
         <v>13.29202663846189</v>
       </c>
     </row>
@@ -1693,6 +1791,9 @@
         </is>
       </c>
       <c r="J33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" t="n">
         <v>13.29202663846189</v>
       </c>
     </row>
@@ -1731,6 +1832,9 @@
         </is>
       </c>
       <c r="J34" t="n">
+        <v>5</v>
+      </c>
+      <c r="K34" t="n">
         <v>13.74461230569916</v>
       </c>
     </row>
@@ -1769,6 +1873,9 @@
         </is>
       </c>
       <c r="J35" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" t="n">
         <v>14.01711486461985</v>
       </c>
     </row>
@@ -1807,6 +1914,9 @@
         </is>
       </c>
       <c r="J36" t="n">
+        <v>5</v>
+      </c>
+      <c r="K36" t="n">
         <v>14.02341868198291</v>
       </c>
     </row>
@@ -1845,6 +1955,9 @@
         </is>
       </c>
       <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
         <v>14.4136984000467</v>
       </c>
     </row>
@@ -1883,6 +1996,9 @@
         </is>
       </c>
       <c r="J38" t="n">
+        <v>5</v>
+      </c>
+      <c r="K38" t="n">
         <v>14.4136984000467</v>
       </c>
     </row>
@@ -1921,6 +2037,9 @@
         </is>
       </c>
       <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
         <v>14.4136984000467</v>
       </c>
     </row>
@@ -1959,6 +2078,9 @@
         </is>
       </c>
       <c r="J40" t="n">
+        <v>5</v>
+      </c>
+      <c r="K40" t="n">
         <v>14.37286417316269</v>
       </c>
     </row>
@@ -1997,6 +2119,9 @@
         </is>
       </c>
       <c r="J41" t="n">
+        <v>5</v>
+      </c>
+      <c r="K41" t="n">
         <v>14.36056284287022</v>
       </c>
     </row>
@@ -2035,6 +2160,9 @@
         </is>
       </c>
       <c r="J42" t="n">
+        <v>5</v>
+      </c>
+      <c r="K42" t="n">
         <v>14.32918239439808</v>
       </c>
     </row>
@@ -2073,6 +2201,9 @@
         </is>
       </c>
       <c r="J43" t="n">
+        <v>5</v>
+      </c>
+      <c r="K43" t="n">
         <v>14.33140447444988</v>
       </c>
     </row>
@@ -2111,6 +2242,9 @@
         </is>
       </c>
       <c r="J44" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" t="n">
         <v>14.33266758623184</v>
       </c>
     </row>
@@ -2149,6 +2283,9 @@
         </is>
       </c>
       <c r="J45" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" t="n">
         <v>14.47432312940295</v>
       </c>
     </row>
@@ -2187,6 +2324,9 @@
         </is>
       </c>
       <c r="J46" t="n">
+        <v>5</v>
+      </c>
+      <c r="K46" t="n">
         <v>14.69408070284003</v>
       </c>
     </row>
@@ -2225,6 +2365,9 @@
         </is>
       </c>
       <c r="J47" t="n">
+        <v>5</v>
+      </c>
+      <c r="K47" t="n">
         <v>14.90097207929845</v>
       </c>
     </row>
@@ -2263,6 +2406,9 @@
         </is>
       </c>
       <c r="J48" t="n">
+        <v>5</v>
+      </c>
+      <c r="K48" t="n">
         <v>14.90097207929845</v>
       </c>
     </row>
@@ -2301,6 +2447,9 @@
         </is>
       </c>
       <c r="J49" t="n">
+        <v>5</v>
+      </c>
+      <c r="K49" t="n">
         <v>15.39058793177672</v>
       </c>
     </row>
@@ -2339,6 +2488,9 @@
         </is>
       </c>
       <c r="J50" t="n">
+        <v>5</v>
+      </c>
+      <c r="K50" t="n">
         <v>15.55279586015389</v>
       </c>
     </row>
@@ -2377,6 +2529,9 @@
         </is>
       </c>
       <c r="J51" t="n">
+        <v>5</v>
+      </c>
+      <c r="K51" t="n">
         <v>16.46410452789935</v>
       </c>
     </row>
@@ -2415,6 +2570,9 @@
         </is>
       </c>
       <c r="J52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
         <v>17.37544874440357</v>
       </c>
     </row>
@@ -2453,6 +2611,9 @@
         </is>
       </c>
       <c r="J53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="n">
         <v>18.99504856873714</v>
       </c>
     </row>
@@ -2491,6 +2652,9 @@
         </is>
       </c>
       <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="n">
         <v>19.35440687995326</v>
       </c>
     </row>
@@ -2529,6 +2693,9 @@
         </is>
       </c>
       <c r="J55" t="n">
+        <v>11</v>
+      </c>
+      <c r="K55" t="n">
         <v>20.44211148955486</v>
       </c>
     </row>
@@ -2567,6 +2734,9 @@
         </is>
       </c>
       <c r="J56" t="n">
+        <v>11</v>
+      </c>
+      <c r="K56" t="n">
         <v>20.85513318717049</v>
       </c>
     </row>
@@ -2605,6 +2775,9 @@
         </is>
       </c>
       <c r="J57" t="n">
+        <v>11</v>
+      </c>
+      <c r="K57" t="n">
         <v>21.24417781615288</v>
       </c>
     </row>
@@ -2643,6 +2816,9 @@
         </is>
       </c>
       <c r="J58" t="n">
+        <v>11</v>
+      </c>
+      <c r="K58" t="n">
         <v>21.57890195439783</v>
       </c>
     </row>
@@ -2681,6 +2857,9 @@
         </is>
       </c>
       <c r="J59" t="n">
+        <v>11</v>
+      </c>
+      <c r="K59" t="n">
         <v>22.69930894948986</v>
       </c>
     </row>
@@ -2719,6 +2898,9 @@
         </is>
       </c>
       <c r="J60" t="n">
+        <v>11</v>
+      </c>
+      <c r="K60" t="n">
         <v>24.17628142732889</v>
       </c>
     </row>
@@ -2757,6 +2939,9 @@
         </is>
       </c>
       <c r="J61" t="n">
+        <v>11</v>
+      </c>
+      <c r="K61" t="n">
         <v>24.17628142732889</v>
       </c>
     </row>
@@ -2795,6 +2980,9 @@
         </is>
       </c>
       <c r="J62" t="n">
+        <v>11</v>
+      </c>
+      <c r="K62" t="n">
         <v>24.17628142732889</v>
       </c>
     </row>
@@ -2833,6 +3021,9 @@
         </is>
       </c>
       <c r="J63" t="n">
+        <v>11</v>
+      </c>
+      <c r="K63" t="n">
         <v>26.20186131343188</v>
       </c>
     </row>
@@ -2871,6 +3062,9 @@
         </is>
       </c>
       <c r="J64" t="n">
+        <v>11</v>
+      </c>
+      <c r="K64" t="n">
         <v>26.20186131343188</v>
       </c>
     </row>
@@ -2909,6 +3103,9 @@
         </is>
       </c>
       <c r="J65" t="n">
+        <v>11</v>
+      </c>
+      <c r="K65" t="n">
         <v>25.66606308824377</v>
       </c>
     </row>
@@ -2947,6 +3144,9 @@
         </is>
       </c>
       <c r="J66" t="n">
+        <v>11</v>
+      </c>
+      <c r="K66" t="n">
         <v>25.66606308824377</v>
       </c>
     </row>
@@ -2985,6 +3185,9 @@
         </is>
       </c>
       <c r="J67" t="n">
+        <v>11</v>
+      </c>
+      <c r="K67" t="n">
         <v>25.66606308824377</v>
       </c>
     </row>
@@ -3023,6 +3226,9 @@
         </is>
       </c>
       <c r="J68" t="n">
+        <v>11</v>
+      </c>
+      <c r="K68" t="n">
         <v>25.66606308824377</v>
       </c>
     </row>
@@ -3061,6 +3267,9 @@
         </is>
       </c>
       <c r="J69" t="n">
+        <v>11</v>
+      </c>
+      <c r="K69" t="n">
         <v>24.51820949168631</v>
       </c>
     </row>
@@ -3099,6 +3308,9 @@
         </is>
       </c>
       <c r="J70" t="n">
+        <v>11</v>
+      </c>
+      <c r="K70" t="n">
         <v>24.17916618470565</v>
       </c>
     </row>
@@ -3137,6 +3349,9 @@
         </is>
       </c>
       <c r="J71" t="n">
+        <v>11</v>
+      </c>
+      <c r="K71" t="n">
         <v>25.5966815762619</v>
       </c>
     </row>
@@ -3175,6 +3390,9 @@
         </is>
       </c>
       <c r="J72" t="n">
+        <v>11</v>
+      </c>
+      <c r="K72" t="n">
         <v>26.88995911838267</v>
       </c>
     </row>
@@ -3213,6 +3431,9 @@
         </is>
       </c>
       <c r="J73" t="n">
+        <v>11</v>
+      </c>
+      <c r="K73" t="n">
         <v>26.88995911838267</v>
       </c>
     </row>
@@ -3251,6 +3472,9 @@
         </is>
       </c>
       <c r="J74" t="n">
+        <v>11</v>
+      </c>
+      <c r="K74" t="n">
         <v>28.52316172484845</v>
       </c>
     </row>
@@ -3289,6 +3513,9 @@
         </is>
       </c>
       <c r="J75" t="n">
+        <v>11</v>
+      </c>
+      <c r="K75" t="n">
         <v>30.66588861137356</v>
       </c>
     </row>
@@ -3327,6 +3554,9 @@
         </is>
       </c>
       <c r="J76" t="n">
+        <v>11</v>
+      </c>
+      <c r="K76" t="n">
         <v>30.66588861137356</v>
       </c>
     </row>
@@ -3365,6 +3595,9 @@
         </is>
       </c>
       <c r="J77" t="n">
+        <v>11</v>
+      </c>
+      <c r="K77" t="n">
         <v>32.12320473761747</v>
       </c>
     </row>
@@ -3403,6 +3636,9 @@
         </is>
       </c>
       <c r="J78" t="n">
+        <v>11</v>
+      </c>
+      <c r="K78" t="n">
         <v>33.20937179433919</v>
       </c>
     </row>
@@ -3441,6 +3677,9 @@
         </is>
       </c>
       <c r="J79" t="n">
+        <v>11</v>
+      </c>
+      <c r="K79" t="n">
         <v>29.94731022881903</v>
       </c>
     </row>
@@ -3479,6 +3718,9 @@
         </is>
       </c>
       <c r="J80" t="n">
+        <v>11</v>
+      </c>
+      <c r="K80" t="n">
         <v>29.94731022881903</v>
       </c>
     </row>
@@ -3517,6 +3759,9 @@
         </is>
       </c>
       <c r="J81" t="n">
+        <v>11</v>
+      </c>
+      <c r="K81" t="n">
         <v>33.25403074862375</v>
       </c>
     </row>
@@ -3555,6 +3800,9 @@
         </is>
       </c>
       <c r="J82" t="n">
+        <v>11</v>
+      </c>
+      <c r="K82" t="n">
         <v>35.74430957912962</v>
       </c>
     </row>
@@ -3593,6 +3841,9 @@
         </is>
       </c>
       <c r="J83" t="n">
+        <v>11</v>
+      </c>
+      <c r="K83" t="n">
         <v>35.22205046464095</v>
       </c>
     </row>
@@ -3631,6 +3882,9 @@
         </is>
       </c>
       <c r="J84" t="n">
+        <v>11</v>
+      </c>
+      <c r="K84" t="n">
         <v>32.3137282444406</v>
       </c>
     </row>
@@ -3669,6 +3923,9 @@
         </is>
       </c>
       <c r="J85" t="n">
+        <v>17</v>
+      </c>
+      <c r="K85" t="n">
         <v>3.655625202153288</v>
       </c>
     </row>
@@ -3707,6 +3964,9 @@
         </is>
       </c>
       <c r="J86" t="n">
+        <v>17</v>
+      </c>
+      <c r="K86" t="n">
         <v>3.264927063259222</v>
       </c>
     </row>
@@ -3745,6 +4005,9 @@
         </is>
       </c>
       <c r="J87" t="n">
+        <v>17</v>
+      </c>
+      <c r="K87" t="n">
         <v>2.399377731464309</v>
       </c>
     </row>
@@ -3783,6 +4046,9 @@
         </is>
       </c>
       <c r="J88" t="n">
+        <v>17</v>
+      </c>
+      <c r="K88" t="n">
         <v>2.355884347339752</v>
       </c>
     </row>
@@ -3821,6 +4087,9 @@
         </is>
       </c>
       <c r="J89" t="n">
+        <v>17</v>
+      </c>
+      <c r="K89" t="n">
         <v>2.252836045045917</v>
       </c>
     </row>
@@ -3859,6 +4128,9 @@
         </is>
       </c>
       <c r="J90" t="n">
+        <v>17</v>
+      </c>
+      <c r="K90" t="n">
         <v>2.21979661522538</v>
       </c>
     </row>
@@ -3897,6 +4169,9 @@
         </is>
       </c>
       <c r="J91" t="n">
+        <v>17</v>
+      </c>
+      <c r="K91" t="n">
         <v>2.252146836654987</v>
       </c>
     </row>
@@ -3935,6 +4210,9 @@
         </is>
       </c>
       <c r="J92" t="n">
+        <v>17</v>
+      </c>
+      <c r="K92" t="n">
         <v>2.30019580561668</v>
       </c>
     </row>
@@ -3973,6 +4251,9 @@
         </is>
       </c>
       <c r="J93" t="n">
+        <v>17</v>
+      </c>
+      <c r="K93" t="n">
         <v>2.352384292151674</v>
       </c>
     </row>
@@ -4011,6 +4292,9 @@
         </is>
       </c>
       <c r="J94" t="n">
+        <v>17</v>
+      </c>
+      <c r="K94" t="n">
         <v>2.352384292151674</v>
       </c>
     </row>
@@ -4049,6 +4333,9 @@
         </is>
       </c>
       <c r="J95" t="n">
+        <v>17</v>
+      </c>
+      <c r="K95" t="n">
         <v>2.550873196243217</v>
       </c>
     </row>
@@ -4087,6 +4374,9 @@
         </is>
       </c>
       <c r="J96" t="n">
+        <v>17</v>
+      </c>
+      <c r="K96" t="n">
         <v>2.550873196243217</v>
       </c>
     </row>
@@ -4125,6 +4415,9 @@
         </is>
       </c>
       <c r="J97" t="n">
+        <v>17</v>
+      </c>
+      <c r="K97" t="n">
         <v>2.550873196243217</v>
       </c>
     </row>
@@ -4163,6 +4456,9 @@
         </is>
       </c>
       <c r="J98" t="n">
+        <v>17</v>
+      </c>
+      <c r="K98" t="n">
         <v>2.550873196243217</v>
       </c>
     </row>
@@ -4201,6 +4497,9 @@
         </is>
       </c>
       <c r="J99" t="n">
+        <v>17</v>
+      </c>
+      <c r="K99" t="n">
         <v>2.653203568705818</v>
       </c>
     </row>
@@ -4239,6 +4538,9 @@
         </is>
       </c>
       <c r="J100" t="n">
+        <v>17</v>
+      </c>
+      <c r="K100" t="n">
         <v>2.643804707830325</v>
       </c>
     </row>
@@ -4277,6 +4579,9 @@
         </is>
       </c>
       <c r="J101" t="n">
+        <v>17</v>
+      </c>
+      <c r="K101" t="n">
         <v>2.418092743267994</v>
       </c>
     </row>
@@ -4315,6 +4620,9 @@
         </is>
       </c>
       <c r="J102" t="n">
+        <v>17</v>
+      </c>
+      <c r="K102" t="n">
         <v>2.342415712804469</v>
       </c>
     </row>
@@ -4353,6 +4661,9 @@
         </is>
       </c>
       <c r="J103" t="n">
+        <v>17</v>
+      </c>
+      <c r="K103" t="n">
         <v>2.342415712804469</v>
       </c>
     </row>
@@ -4391,6 +4702,9 @@
         </is>
       </c>
       <c r="J104" t="n">
+        <v>17</v>
+      </c>
+      <c r="K104" t="n">
         <v>2.268576143173112</v>
       </c>
     </row>
@@ -4429,6 +4743,9 @@
         </is>
       </c>
       <c r="J105" t="n">
+        <v>17</v>
+      </c>
+      <c r="K105" t="n">
         <v>2.268576143173112</v>
       </c>
     </row>
@@ -4467,6 +4784,9 @@
         </is>
       </c>
       <c r="J106" t="n">
+        <v>17</v>
+      </c>
+      <c r="K106" t="n">
         <v>2.217132450735882</v>
       </c>
     </row>
@@ -4505,6 +4825,9 @@
         </is>
       </c>
       <c r="J107" t="n">
+        <v>17</v>
+      </c>
+      <c r="K107" t="n">
         <v>2.2116895385719</v>
       </c>
     </row>
@@ -4543,6 +4866,9 @@
         </is>
       </c>
       <c r="J108" t="n">
+        <v>17</v>
+      </c>
+      <c r="K108" t="n">
         <v>2.205518959400552</v>
       </c>
     </row>
@@ -4581,6 +4907,9 @@
         </is>
       </c>
       <c r="J109" t="n">
+        <v>17</v>
+      </c>
+      <c r="K109" t="n">
         <v>2.185617419654481</v>
       </c>
     </row>
@@ -4619,6 +4948,9 @@
         </is>
       </c>
       <c r="J110" t="n">
+        <v>17</v>
+      </c>
+      <c r="K110" t="n">
         <v>2.155007908898329</v>
       </c>
     </row>
@@ -4657,6 +4989,9 @@
         </is>
       </c>
       <c r="J111" t="n">
+        <v>17</v>
+      </c>
+      <c r="K111" t="n">
         <v>2.121820681858065</v>
       </c>
     </row>
@@ -4695,6 +5030,9 @@
         </is>
       </c>
       <c r="J112" t="n">
+        <v>17</v>
+      </c>
+      <c r="K112" t="n">
         <v>2.121820681858065</v>
       </c>
     </row>
@@ -4733,6 +5071,9 @@
         </is>
       </c>
       <c r="J113" t="n">
+        <v>17</v>
+      </c>
+      <c r="K113" t="n">
         <v>2.249804039781183</v>
       </c>
     </row>
@@ -4771,6 +5112,9 @@
         </is>
       </c>
       <c r="J114" t="n">
+        <v>17</v>
+      </c>
+      <c r="K114" t="n">
         <v>2.276935456485526</v>
       </c>
     </row>
@@ -4809,6 +5153,9 @@
         </is>
       </c>
       <c r="J115" t="n">
+        <v>17</v>
+      </c>
+      <c r="K115" t="n">
         <v>2.294309311820022</v>
       </c>
     </row>
@@ -4847,6 +5194,9 @@
         </is>
       </c>
       <c r="J116" t="n">
+        <v>17</v>
+      </c>
+      <c r="K116" t="n">
         <v>2.313323918834337</v>
       </c>
     </row>
@@ -4885,6 +5235,9 @@
         </is>
       </c>
       <c r="J117" t="n">
+        <v>17</v>
+      </c>
+      <c r="K117" t="n">
         <v>2.313323918834337</v>
       </c>
     </row>
@@ -4923,6 +5276,9 @@
         </is>
       </c>
       <c r="J118" t="n">
+        <v>17</v>
+      </c>
+      <c r="K118" t="n">
         <v>2.319676220724453</v>
       </c>
     </row>
@@ -4961,6 +5317,9 @@
         </is>
       </c>
       <c r="J119" t="n">
+        <v>17</v>
+      </c>
+      <c r="K119" t="n">
         <v>2.282193623509603</v>
       </c>
     </row>
@@ -4999,6 +5358,9 @@
         </is>
       </c>
       <c r="J120" t="n">
+        <v>17</v>
+      </c>
+      <c r="K120" t="n">
         <v>2.261802382317713</v>
       </c>
     </row>
@@ -5037,6 +5399,9 @@
         </is>
       </c>
       <c r="J121" t="n">
+        <v>17</v>
+      </c>
+      <c r="K121" t="n">
         <v>2.255876719294342</v>
       </c>
     </row>
@@ -5075,6 +5440,9 @@
         </is>
       </c>
       <c r="J122" t="n">
+        <v>17</v>
+      </c>
+      <c r="K122" t="n">
         <v>2.255876719294342</v>
       </c>
     </row>
@@ -5113,6 +5481,9 @@
         </is>
       </c>
       <c r="J123" t="n">
+        <v>17</v>
+      </c>
+      <c r="K123" t="n">
         <v>2.278145012965538</v>
       </c>
     </row>
@@ -5151,6 +5522,9 @@
         </is>
       </c>
       <c r="J124" t="n">
+        <v>17</v>
+      </c>
+      <c r="K124" t="n">
         <v>2.278145012965538</v>
       </c>
     </row>
@@ -5189,6 +5563,9 @@
         </is>
       </c>
       <c r="J125" t="n">
+        <v>17</v>
+      </c>
+      <c r="K125" t="n">
         <v>2.29998581674779</v>
       </c>
     </row>
@@ -5227,6 +5604,9 @@
         </is>
       </c>
       <c r="J126" t="n">
+        <v>17</v>
+      </c>
+      <c r="K126" t="n">
         <v>2.39899655611404</v>
       </c>
     </row>
@@ -5265,6 +5645,9 @@
         </is>
       </c>
       <c r="J127" t="n">
+        <v>17</v>
+      </c>
+      <c r="K127" t="n">
         <v>2.426003596047259</v>
       </c>
     </row>
@@ -5303,6 +5686,9 @@
         </is>
       </c>
       <c r="J128" t="n">
+        <v>17</v>
+      </c>
+      <c r="K128" t="n">
         <v>2.43304178777875</v>
       </c>
     </row>
@@ -5341,6 +5727,9 @@
         </is>
       </c>
       <c r="J129" t="n">
+        <v>17</v>
+      </c>
+      <c r="K129" t="n">
         <v>2.329533845651123</v>
       </c>
     </row>
@@ -5379,6 +5768,9 @@
         </is>
       </c>
       <c r="J130" t="n">
+        <v>17</v>
+      </c>
+      <c r="K130" t="n">
         <v>2.329533845651123</v>
       </c>
     </row>
@@ -5417,6 +5809,9 @@
         </is>
       </c>
       <c r="J131" t="n">
+        <v>17</v>
+      </c>
+      <c r="K131" t="n">
         <v>2.329533845651123</v>
       </c>
     </row>
@@ -5455,6 +5850,9 @@
         </is>
       </c>
       <c r="J132" t="n">
+        <v>17</v>
+      </c>
+      <c r="K132" t="n">
         <v>2.275503708438266</v>
       </c>
     </row>
@@ -5493,6 +5891,9 @@
         </is>
       </c>
       <c r="J133" t="n">
+        <v>17</v>
+      </c>
+      <c r="K133" t="n">
         <v>2.129964220088542</v>
       </c>
     </row>
@@ -5531,6 +5932,9 @@
         </is>
       </c>
       <c r="J134" t="n">
+        <v>17</v>
+      </c>
+      <c r="K134" t="n">
         <v>1.726676601806959</v>
       </c>
     </row>
@@ -5569,6 +5973,9 @@
         </is>
       </c>
       <c r="J135" t="n">
+        <v>17</v>
+      </c>
+      <c r="K135" t="n">
         <v>1.726676601806959</v>
       </c>
     </row>
@@ -5607,6 +6014,9 @@
         </is>
       </c>
       <c r="J136" t="n">
+        <v>17</v>
+      </c>
+      <c r="K136" t="n">
         <v>1.604021776767994</v>
       </c>
     </row>
@@ -5645,6 +6055,9 @@
         </is>
       </c>
       <c r="J137" t="n">
+        <v>17</v>
+      </c>
+      <c r="K137" t="n">
         <v>1.495663010984039</v>
       </c>
     </row>
@@ -5683,6 +6096,9 @@
         </is>
       </c>
       <c r="J138" t="n">
+        <v>17</v>
+      </c>
+      <c r="K138" t="n">
         <v>1.495663010984039</v>
       </c>
     </row>
@@ -5721,6 +6137,9 @@
         </is>
       </c>
       <c r="J139" t="n">
+        <v>17</v>
+      </c>
+      <c r="K139" t="n">
         <v>1.140911278710099</v>
       </c>
     </row>
@@ -5759,6 +6178,9 @@
         </is>
       </c>
       <c r="J140" t="n">
+        <v>17</v>
+      </c>
+      <c r="K140" t="n">
         <v>0.9804261502569596</v>
       </c>
     </row>
@@ -5797,6 +6219,9 @@
         </is>
       </c>
       <c r="J141" t="n">
+        <v>17</v>
+      </c>
+      <c r="K141" t="n">
         <v>0.947668382193923</v>
       </c>
     </row>
@@ -5835,6 +6260,9 @@
         </is>
       </c>
       <c r="J142" t="n">
+        <v>17</v>
+      </c>
+      <c r="K142" t="n">
         <v>1.046449695602111</v>
       </c>
     </row>
@@ -5873,6 +6301,9 @@
         </is>
       </c>
       <c r="J143" t="n">
+        <v>17</v>
+      </c>
+      <c r="K143" t="n">
         <v>1.046449695602111</v>
       </c>
     </row>
@@ -5911,6 +6342,9 @@
         </is>
       </c>
       <c r="J144" t="n">
+        <v>17</v>
+      </c>
+      <c r="K144" t="n">
         <v>1.094491209829949</v>
       </c>
     </row>
@@ -5949,6 +6383,9 @@
         </is>
       </c>
       <c r="J145" t="n">
+        <v>17</v>
+      </c>
+      <c r="K145" t="n">
         <v>1.121456763951091</v>
       </c>
     </row>
@@ -5987,6 +6424,9 @@
         </is>
       </c>
       <c r="J146" t="n">
+        <v>17</v>
+      </c>
+      <c r="K146" t="n">
         <v>1.160223779553904</v>
       </c>
     </row>
@@ -6025,6 +6465,9 @@
         </is>
       </c>
       <c r="J147" t="n">
+        <v>17</v>
+      </c>
+      <c r="K147" t="n">
         <v>1.427812544501824</v>
       </c>
     </row>
@@ -6063,6 +6506,9 @@
         </is>
       </c>
       <c r="J148" t="n">
+        <v>17</v>
+      </c>
+      <c r="K148" t="n">
         <v>1.427812544501824</v>
       </c>
     </row>
@@ -6101,6 +6547,9 @@
         </is>
       </c>
       <c r="J149" t="n">
+        <v>17</v>
+      </c>
+      <c r="K149" t="n">
         <v>1.755441115818343</v>
       </c>
     </row>
@@ -6139,6 +6588,9 @@
         </is>
       </c>
       <c r="J150" t="n">
+        <v>17</v>
+      </c>
+      <c r="K150" t="n">
         <v>1.755441115818343</v>
       </c>
     </row>
@@ -6177,6 +6629,9 @@
         </is>
       </c>
       <c r="J151" t="n">
+        <v>17</v>
+      </c>
+      <c r="K151" t="n">
         <v>1.788673379144996</v>
       </c>
     </row>
@@ -6215,6 +6670,9 @@
         </is>
       </c>
       <c r="J152" t="n">
+        <v>17</v>
+      </c>
+      <c r="K152" t="n">
         <v>1.778274352829337</v>
       </c>
     </row>
@@ -6253,6 +6711,9 @@
         </is>
       </c>
       <c r="J153" t="n">
+        <v>17</v>
+      </c>
+      <c r="K153" t="n">
         <v>1.778274352829337</v>
       </c>
     </row>
@@ -6291,6 +6752,9 @@
         </is>
       </c>
       <c r="J154" t="n">
+        <v>17</v>
+      </c>
+      <c r="K154" t="n">
         <v>1.772817011596296</v>
       </c>
     </row>
@@ -6329,6 +6793,9 @@
         </is>
       </c>
       <c r="J155" t="n">
+        <v>17</v>
+      </c>
+      <c r="K155" t="n">
         <v>1.752865128020558</v>
       </c>
     </row>
@@ -6367,6 +6834,9 @@
         </is>
       </c>
       <c r="J156" t="n">
+        <v>17</v>
+      </c>
+      <c r="K156" t="n">
         <v>1.701855296213878</v>
       </c>
     </row>
@@ -6405,6 +6875,9 @@
         </is>
       </c>
       <c r="J157" t="n">
+        <v>17</v>
+      </c>
+      <c r="K157" t="n">
         <v>1.39792805562581</v>
       </c>
     </row>
@@ -6443,6 +6916,9 @@
         </is>
       </c>
       <c r="J158" t="n">
+        <v>17</v>
+      </c>
+      <c r="K158" t="n">
         <v>1.39792805562581</v>
       </c>
     </row>
@@ -6481,6 +6957,9 @@
         </is>
       </c>
       <c r="J159" t="n">
+        <v>17</v>
+      </c>
+      <c r="K159" t="n">
         <v>1.327320467937538</v>
       </c>
     </row>
@@ -6519,6 +6998,9 @@
         </is>
       </c>
       <c r="J160" t="n">
+        <v>17</v>
+      </c>
+      <c r="K160" t="n">
         <v>1.1971891976014</v>
       </c>
     </row>
@@ -6557,6 +7039,9 @@
         </is>
       </c>
       <c r="J161" t="n">
+        <v>17</v>
+      </c>
+      <c r="K161" t="n">
         <v>1.1971891976014</v>
       </c>
     </row>
@@ -6595,6 +7080,9 @@
         </is>
       </c>
       <c r="J162" t="n">
+        <v>17</v>
+      </c>
+      <c r="K162" t="n">
         <v>1.1971891976014</v>
       </c>
     </row>
@@ -6633,6 +7121,9 @@
         </is>
       </c>
       <c r="J163" t="n">
+        <v>17</v>
+      </c>
+      <c r="K163" t="n">
         <v>1.144755081883404</v>
       </c>
     </row>
@@ -6671,6 +7162,9 @@
         </is>
       </c>
       <c r="J164" t="n">
+        <v>17</v>
+      </c>
+      <c r="K164" t="n">
         <v>1.110326020176739</v>
       </c>
     </row>
@@ -6709,6 +7203,9 @@
         </is>
       </c>
       <c r="J165" t="n">
+        <v>17</v>
+      </c>
+      <c r="K165" t="n">
         <v>1.127592304758405</v>
       </c>
     </row>
@@ -6747,6 +7244,9 @@
         </is>
       </c>
       <c r="J166" t="n">
+        <v>17</v>
+      </c>
+      <c r="K166" t="n">
         <v>1.129235734728124</v>
       </c>
     </row>
@@ -6785,6 +7285,9 @@
         </is>
       </c>
       <c r="J167" t="n">
+        <v>17</v>
+      </c>
+      <c r="K167" t="n">
         <v>1.129235734728124</v>
       </c>
     </row>
@@ -6823,6 +7326,9 @@
         </is>
       </c>
       <c r="J168" t="n">
+        <v>17</v>
+      </c>
+      <c r="K168" t="n">
         <v>1.129235734728124</v>
       </c>
     </row>
@@ -6861,6 +7367,9 @@
         </is>
       </c>
       <c r="J169" t="n">
+        <v>17</v>
+      </c>
+      <c r="K169" t="n">
         <v>1.07931209195279</v>
       </c>
     </row>
@@ -6899,6 +7408,9 @@
         </is>
       </c>
       <c r="J170" t="n">
+        <v>17</v>
+      </c>
+      <c r="K170" t="n">
         <v>1.007523819185527</v>
       </c>
     </row>
@@ -6937,6 +7449,9 @@
         </is>
       </c>
       <c r="J171" t="n">
+        <v>17</v>
+      </c>
+      <c r="K171" t="n">
         <v>0.9898694112683336</v>
       </c>
     </row>
@@ -6975,6 +7490,9 @@
         </is>
       </c>
       <c r="J172" t="n">
+        <v>17</v>
+      </c>
+      <c r="K172" t="n">
         <v>0.9914543051707039</v>
       </c>
     </row>
@@ -7013,6 +7531,9 @@
         </is>
       </c>
       <c r="J173" t="n">
+        <v>17</v>
+      </c>
+      <c r="K173" t="n">
         <v>0.9914543051707039</v>
       </c>
     </row>
@@ -7051,6 +7572,9 @@
         </is>
       </c>
       <c r="J174" t="n">
+        <v>17</v>
+      </c>
+      <c r="K174" t="n">
         <v>1.06923049452409</v>
       </c>
     </row>
@@ -7089,6 +7613,9 @@
         </is>
       </c>
       <c r="J175" t="n">
+        <v>17</v>
+      </c>
+      <c r="K175" t="n">
         <v>1.187175472566269</v>
       </c>
     </row>
@@ -7127,6 +7654,9 @@
         </is>
       </c>
       <c r="J176" t="n">
+        <v>17</v>
+      </c>
+      <c r="K176" t="n">
         <v>1.333556077280552</v>
       </c>
     </row>
@@ -7165,6 +7695,9 @@
         </is>
       </c>
       <c r="J177" t="n">
+        <v>17</v>
+      </c>
+      <c r="K177" t="n">
         <v>1.312922373703677</v>
       </c>
     </row>
@@ -7203,6 +7736,9 @@
         </is>
       </c>
       <c r="J178" t="n">
+        <v>17</v>
+      </c>
+      <c r="K178" t="n">
         <v>1.269293198848958</v>
       </c>
     </row>
@@ -7241,6 +7777,9 @@
         </is>
       </c>
       <c r="J179" t="n">
+        <v>17</v>
+      </c>
+      <c r="K179" t="n">
         <v>1.269293198848958</v>
       </c>
     </row>
@@ -7279,6 +7818,9 @@
         </is>
       </c>
       <c r="J180" t="n">
+        <v>17</v>
+      </c>
+      <c r="K180" t="n">
         <v>1.167607646918589</v>
       </c>
     </row>
@@ -7317,6 +7859,9 @@
         </is>
       </c>
       <c r="J181" t="n">
+        <v>17</v>
+      </c>
+      <c r="K181" t="n">
         <v>1.058335978988722</v>
       </c>
     </row>
@@ -7355,6 +7900,9 @@
         </is>
       </c>
       <c r="J182" t="n">
+        <v>17</v>
+      </c>
+      <c r="K182" t="n">
         <v>1.072186129913543</v>
       </c>
     </row>
@@ -7393,6 +7941,9 @@
         </is>
       </c>
       <c r="J183" t="n">
+        <v>17</v>
+      </c>
+      <c r="K183" t="n">
         <v>1.104115376478233</v>
       </c>
     </row>
@@ -7431,6 +7982,9 @@
         </is>
       </c>
       <c r="J184" t="n">
+        <v>17</v>
+      </c>
+      <c r="K184" t="n">
         <v>1.141062351849522</v>
       </c>
     </row>
@@ -7469,6 +8023,9 @@
         </is>
       </c>
       <c r="J185" t="n">
+        <v>17</v>
+      </c>
+      <c r="K185" t="n">
         <v>1.191043762367248</v>
       </c>
     </row>
@@ -7507,6 +8064,9 @@
         </is>
       </c>
       <c r="J186" t="n">
+        <v>17</v>
+      </c>
+      <c r="K186" t="n">
         <v>1.191043762367248</v>
       </c>
     </row>
@@ -7545,6 +8105,9 @@
         </is>
       </c>
       <c r="J187" t="n">
+        <v>17</v>
+      </c>
+      <c r="K187" t="n">
         <v>1.486028554703088</v>
       </c>
     </row>
@@ -7583,6 +8146,9 @@
         </is>
       </c>
       <c r="J188" t="n">
+        <v>17</v>
+      </c>
+      <c r="K188" t="n">
         <v>1.547807787268301</v>
       </c>
     </row>
@@ -7621,6 +8187,9 @@
         </is>
       </c>
       <c r="J189" t="n">
+        <v>17</v>
+      </c>
+      <c r="K189" t="n">
         <v>1.844475967958824</v>
       </c>
     </row>
@@ -7659,6 +8228,9 @@
         </is>
       </c>
       <c r="J190" t="n">
+        <v>17</v>
+      </c>
+      <c r="K190" t="n">
         <v>1.841571538570617</v>
       </c>
     </row>
@@ -7697,6 +8269,9 @@
         </is>
       </c>
       <c r="J191" t="n">
+        <v>17</v>
+      </c>
+      <c r="K191" t="n">
         <v>1.841571538570617</v>
       </c>
     </row>
@@ -7735,6 +8310,9 @@
         </is>
       </c>
       <c r="J192" t="n">
+        <v>17</v>
+      </c>
+      <c r="K192" t="n">
         <v>1.720576971928573</v>
       </c>
     </row>
@@ -7773,6 +8351,9 @@
         </is>
       </c>
       <c r="J193" t="n">
+        <v>17</v>
+      </c>
+      <c r="K193" t="n">
         <v>1.643774409243683</v>
       </c>
     </row>
@@ -7811,6 +8392,9 @@
         </is>
       </c>
       <c r="J194" t="n">
+        <v>17</v>
+      </c>
+      <c r="K194" t="n">
         <v>1.643774409243683</v>
       </c>
     </row>
@@ -7849,6 +8433,9 @@
         </is>
       </c>
       <c r="J195" t="n">
+        <v>17</v>
+      </c>
+      <c r="K195" t="n">
         <v>1.555805184715616</v>
       </c>
     </row>
@@ -7887,6 +8474,9 @@
         </is>
       </c>
       <c r="J196" t="n">
+        <v>17</v>
+      </c>
+      <c r="K196" t="n">
         <v>1.278466120075154</v>
       </c>
     </row>
@@ -7925,6 +8515,9 @@
         </is>
       </c>
       <c r="J197" t="n">
+        <v>17</v>
+      </c>
+      <c r="K197" t="n">
         <v>1.200149342274758</v>
       </c>
     </row>
@@ -7963,6 +8556,9 @@
         </is>
       </c>
       <c r="J198" t="n">
+        <v>17</v>
+      </c>
+      <c r="K198" t="n">
         <v>0.8658938311966332</v>
       </c>
     </row>
@@ -8001,6 +8597,9 @@
         </is>
       </c>
       <c r="J199" t="n">
+        <v>17</v>
+      </c>
+      <c r="K199" t="n">
         <v>0.8658938311966332</v>
       </c>
     </row>
@@ -8039,6 +8638,9 @@
         </is>
       </c>
       <c r="J200" t="n">
+        <v>17</v>
+      </c>
+      <c r="K200" t="n">
         <v>0.8658938311966332</v>
       </c>
     </row>
@@ -8077,6 +8679,9 @@
         </is>
       </c>
       <c r="J201" t="n">
+        <v>17</v>
+      </c>
+      <c r="K201" t="n">
         <v>0.7954039355764896</v>
       </c>
     </row>
@@ -8115,6 +8720,9 @@
         </is>
       </c>
       <c r="J202" t="n">
+        <v>17</v>
+      </c>
+      <c r="K202" t="n">
         <v>0.6192300669665526</v>
       </c>
     </row>
@@ -8153,6 +8761,9 @@
         </is>
       </c>
       <c r="J203" t="n">
+        <v>17</v>
+      </c>
+      <c r="K203" t="n">
         <v>0.5385163421711662</v>
       </c>
     </row>
@@ -8191,6 +8802,9 @@
         </is>
       </c>
       <c r="J204" t="n">
+        <v>17</v>
+      </c>
+      <c r="K204" t="n">
         <v>0.4522874703617749</v>
       </c>
     </row>
@@ -8229,6 +8843,9 @@
         </is>
       </c>
       <c r="J205" t="n">
+        <v>17</v>
+      </c>
+      <c r="K205" t="n">
         <v>0.4322579786603727</v>
       </c>
     </row>
@@ -8267,6 +8884,9 @@
         </is>
       </c>
       <c r="J206" t="n">
+        <v>17</v>
+      </c>
+      <c r="K206" t="n">
         <v>0.4041573121506322</v>
       </c>
     </row>
@@ -8305,6 +8925,9 @@
         </is>
       </c>
       <c r="J207" t="n">
+        <v>17</v>
+      </c>
+      <c r="K207" t="n">
         <v>0.4213399913646258</v>
       </c>
     </row>
@@ -8343,6 +8966,9 @@
         </is>
       </c>
       <c r="J208" t="n">
+        <v>17</v>
+      </c>
+      <c r="K208" t="n">
         <v>0.470025857502466</v>
       </c>
     </row>
@@ -8381,6 +9007,9 @@
         </is>
       </c>
       <c r="J209" t="n">
+        <v>17</v>
+      </c>
+      <c r="K209" t="n">
         <v>0.6684152252175423</v>
       </c>
     </row>
@@ -8419,6 +9048,9 @@
         </is>
       </c>
       <c r="J210" t="n">
+        <v>17</v>
+      </c>
+      <c r="K210" t="n">
         <v>0.7179541259534254</v>
       </c>
     </row>
@@ -8457,6 +9089,9 @@
         </is>
       </c>
       <c r="J211" t="n">
+        <v>17</v>
+      </c>
+      <c r="K211" t="n">
         <v>0.7179541259534254</v>
       </c>
     </row>
@@ -8495,6 +9130,9 @@
         </is>
       </c>
       <c r="J212" t="n">
+        <v>17</v>
+      </c>
+      <c r="K212" t="n">
         <v>0.7179541259534254</v>
       </c>
     </row>
@@ -8533,6 +9171,9 @@
         </is>
       </c>
       <c r="J213" t="n">
+        <v>17</v>
+      </c>
+      <c r="K213" t="n">
         <v>0.8504789130187842</v>
       </c>
     </row>
@@ -8571,6 +9212,9 @@
         </is>
       </c>
       <c r="J214" t="n">
+        <v>17</v>
+      </c>
+      <c r="K214" t="n">
         <v>0.8504789130187842</v>
       </c>
     </row>
@@ -8609,6 +9253,9 @@
         </is>
       </c>
       <c r="J215" t="n">
+        <v>17</v>
+      </c>
+      <c r="K215" t="n">
         <v>0.902790715459413</v>
       </c>
     </row>
@@ -8647,6 +9294,9 @@
         </is>
       </c>
       <c r="J216" t="n">
+        <v>17</v>
+      </c>
+      <c r="K216" t="n">
         <v>0.902790715459413</v>
       </c>
     </row>
@@ -8685,6 +9335,9 @@
         </is>
       </c>
       <c r="J217" t="n">
+        <v>17</v>
+      </c>
+      <c r="K217" t="n">
         <v>0.9315183779958096</v>
       </c>
     </row>
@@ -8723,6 +9376,9 @@
         </is>
       </c>
       <c r="J218" t="n">
+        <v>17</v>
+      </c>
+      <c r="K218" t="n">
         <v>0.9315183779958096</v>
       </c>
     </row>
@@ -8761,6 +9417,9 @@
         </is>
       </c>
       <c r="J219" t="n">
+        <v>17</v>
+      </c>
+      <c r="K219" t="n">
         <v>0.8851152668858296</v>
       </c>
     </row>
@@ -8799,6 +9458,9 @@
         </is>
       </c>
       <c r="J220" t="n">
+        <v>17</v>
+      </c>
+      <c r="K220" t="n">
         <v>0.8426817177160192</v>
       </c>
     </row>
@@ -8837,6 +9499,9 @@
         </is>
       </c>
       <c r="J221" t="n">
+        <v>17</v>
+      </c>
+      <c r="K221" t="n">
         <v>0.6938713116664846</v>
       </c>
     </row>
@@ -8875,6 +9540,9 @@
         </is>
       </c>
       <c r="J222" t="n">
+        <v>17</v>
+      </c>
+      <c r="K222" t="n">
         <v>0.6938713116664846</v>
       </c>
     </row>
@@ -8913,6 +9581,9 @@
         </is>
       </c>
       <c r="J223" t="n">
+        <v>17</v>
+      </c>
+      <c r="K223" t="n">
         <v>0.5629841550136426</v>
       </c>
     </row>
@@ -8951,6 +9622,9 @@
         </is>
       </c>
       <c r="J224" t="n">
+        <v>17</v>
+      </c>
+      <c r="K224" t="n">
         <v>0.5463302263033294</v>
       </c>
     </row>
@@ -8989,6 +9663,9 @@
         </is>
       </c>
       <c r="J225" t="n">
+        <v>17</v>
+      </c>
+      <c r="K225" t="n">
         <v>0.5389585101632535</v>
       </c>
     </row>
@@ -9027,6 +9704,9 @@
         </is>
       </c>
       <c r="J226" t="n">
+        <v>17</v>
+      </c>
+      <c r="K226" t="n">
         <v>0.552547338455138</v>
       </c>
     </row>
@@ -9065,6 +9745,9 @@
         </is>
       </c>
       <c r="J227" t="n">
+        <v>17</v>
+      </c>
+      <c r="K227" t="n">
         <v>0.6865475192796013</v>
       </c>
     </row>
@@ -9103,6 +9786,9 @@
         </is>
       </c>
       <c r="J228" t="n">
+        <v>17</v>
+      </c>
+      <c r="K228" t="n">
         <v>0.7107101364517812</v>
       </c>
     </row>
@@ -9141,6 +9827,9 @@
         </is>
       </c>
       <c r="J229" t="n">
+        <v>17</v>
+      </c>
+      <c r="K229" t="n">
         <v>0.6353390966846304</v>
       </c>
     </row>
@@ -9179,6 +9868,9 @@
         </is>
       </c>
       <c r="J230" t="n">
+        <v>17</v>
+      </c>
+      <c r="K230" t="n">
         <v>0.6353390966846304</v>
       </c>
     </row>
@@ -9217,6 +9909,9 @@
         </is>
       </c>
       <c r="J231" t="n">
+        <v>17</v>
+      </c>
+      <c r="K231" t="n">
         <v>0.5467863697612891</v>
       </c>
     </row>
@@ -9255,6 +9950,9 @@
         </is>
       </c>
       <c r="J232" t="n">
+        <v>17</v>
+      </c>
+      <c r="K232" t="n">
         <v>0.5467863697612891</v>
       </c>
     </row>
@@ -9293,6 +9991,9 @@
         </is>
       </c>
       <c r="J233" t="n">
+        <v>17</v>
+      </c>
+      <c r="K233" t="n">
         <v>0.5296327060372106</v>
       </c>
     </row>
@@ -9331,6 +10032,9 @@
         </is>
       </c>
       <c r="J234" t="n">
+        <v>17</v>
+      </c>
+      <c r="K234" t="n">
         <v>0.5371389694150598</v>
       </c>
     </row>
@@ -9369,6 +10073,9 @@
         </is>
       </c>
       <c r="J235" t="n">
+        <v>17</v>
+      </c>
+      <c r="K235" t="n">
         <v>0.5292845606250567</v>
       </c>
     </row>
@@ -9407,6 +10114,9 @@
         </is>
       </c>
       <c r="J236" t="n">
+        <v>17</v>
+      </c>
+      <c r="K236" t="n">
         <v>0.4468478738436192</v>
       </c>
     </row>
@@ -9445,6 +10155,9 @@
         </is>
       </c>
       <c r="J237" t="n">
+        <v>17</v>
+      </c>
+      <c r="K237" t="n">
         <v>0.4468478738436192</v>
       </c>
     </row>
@@ -9483,6 +10196,9 @@
         </is>
       </c>
       <c r="J238" t="n">
+        <v>17</v>
+      </c>
+      <c r="K238" t="n">
         <v>0.3239816099842603</v>
       </c>
     </row>
@@ -9521,6 +10237,9 @@
         </is>
       </c>
       <c r="J239" t="n">
+        <v>17</v>
+      </c>
+      <c r="K239" t="n">
         <v>0.2751216794231886</v>
       </c>
     </row>
@@ -9559,6 +10278,9 @@
         </is>
       </c>
       <c r="J240" t="n">
+        <v>17</v>
+      </c>
+      <c r="K240" t="n">
         <v>0.161947049349651</v>
       </c>
     </row>
@@ -9597,6 +10319,9 @@
         </is>
       </c>
       <c r="J241" t="n">
+        <v>17</v>
+      </c>
+      <c r="K241" t="n">
         <v>0.1422140172117248</v>
       </c>
     </row>
@@ -9635,6 +10360,9 @@
         </is>
       </c>
       <c r="J242" t="n">
+        <v>17</v>
+      </c>
+      <c r="K242" t="n">
         <v>0.1229816940742976</v>
       </c>
     </row>
@@ -9673,6 +10401,9 @@
         </is>
       </c>
       <c r="J243" t="n">
+        <v>17</v>
+      </c>
+      <c r="K243" t="n">
         <v>0.09075891683619514</v>
       </c>
     </row>
@@ -9711,6 +10442,9 @@
         </is>
       </c>
       <c r="J244" t="n">
+        <v>17</v>
+      </c>
+      <c r="K244" t="n">
         <v>0.06090024786127952</v>
       </c>
     </row>

--- a/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B07_Normal_1.xlsx
+++ b/results/block2_results/area/Normal_1/branches/dataframes/dataset_LCA_B07_Normal_1.xlsx
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>24.44938674448072</v>
+        <v>22.73756640125236</v>
       </c>
     </row>
     <row r="3">
@@ -564,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>23.09469567725773</v>
+        <v>21.58556205050919</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>16.22537890841612</v>
+        <v>16.29324050952215</v>
       </c>
     </row>
     <row r="7">
@@ -728,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>15.92519383307983</v>
+        <v>15.99543613326018</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>15.55123726155539</v>
+        <v>15.62439489880449</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>15.50392193361757</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>15.43409332138252</v>
+        <v>15.51994773639756</v>
       </c>
     </row>
     <row r="12">
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86969785602394</v>
       </c>
     </row>
     <row r="13">
@@ -974,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>14.91383648998964</v>
+        <v>14.86959415022024</v>
       </c>
     </row>
     <row r="14">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>13.96252814601202</v>
+        <v>13.91864954866779</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>12.8845474029381</v>
+        <v>12.87463469178007</v>
       </c>
     </row>
     <row r="16">
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>12.56557511094277</v>
+        <v>12.56213898660848</v>
       </c>
     </row>
     <row r="17">
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>12.56557511094277</v>
+        <v>12.55954078162074</v>
       </c>
     </row>
     <row r="18">
@@ -1179,7 +1179,7 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>12.42650727241244</v>
+        <v>12.41804037237105</v>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>12.61222121789064</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="20">
@@ -1261,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="21">
@@ -1302,7 +1302,7 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>12.6149723565889</v>
+        <v>12.61235401004429</v>
       </c>
     </row>
     <row r="22">
@@ -1343,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>12.88726856229838</v>
+        <v>12.89114719647669</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>13.08268414389388</v>
+        <v>13.08601325120547</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>13.11655963642752</v>
+        <v>13.1112961343127</v>
       </c>
     </row>
     <row r="25">
@@ -1466,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>13.06477406907523</v>
+        <v>13.06050754757873</v>
       </c>
     </row>
     <row r="26">
@@ -1507,7 +1507,7 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
     </row>
     <row r="27">
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>13.00822550737505</v>
+        <v>13.00560877247013</v>
       </c>
     </row>
     <row r="28">
@@ -1589,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>12.82946633796654</v>
+        <v>12.82287865109407</v>
       </c>
     </row>
     <row r="29">
@@ -1630,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>12.72199060197538</v>
+        <v>12.71927945377958</v>
       </c>
     </row>
     <row r="30">
@@ -1671,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>12.76786570293602</v>
+        <v>12.77031387086443</v>
       </c>
     </row>
     <row r="31">
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>12.94918332241907</v>
+        <v>12.95485717835137</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29520804089071</v>
       </c>
     </row>
     <row r="33">
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>13.29202663846189</v>
+        <v>13.29710102990174</v>
       </c>
     </row>
     <row r="34">
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>13.74461230569916</v>
+        <v>13.75403391875815</v>
       </c>
     </row>
     <row r="35">
@@ -1876,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>14.01711486461985</v>
+        <v>14.02366076953313</v>
       </c>
     </row>
     <row r="36">
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>14.02341868198291</v>
+        <v>14.02914779581027</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
     </row>
     <row r="38">
@@ -1999,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
     </row>
     <row r="39">
@@ -2040,7 +2040,7 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>14.4136984000467</v>
+        <v>14.4135370281724</v>
       </c>
     </row>
     <row r="40">
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>14.37286417316269</v>
+        <v>14.37156478609048</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>14.36056284287022</v>
+        <v>14.36020323793898</v>
       </c>
     </row>
     <row r="42">
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>14.32918239439808</v>
+        <v>14.3290624341717</v>
       </c>
     </row>
     <row r="43">
@@ -2204,7 +2204,7 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>14.33140447444988</v>
+        <v>14.3325069672442</v>
       </c>
     </row>
     <row r="44">
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>14.33266758623184</v>
+        <v>14.33386682670858</v>
       </c>
     </row>
     <row r="45">
@@ -2286,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>14.47432312940295</v>
+        <v>14.4778957262455</v>
       </c>
     </row>
     <row r="46">
@@ -2327,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>14.69408070284003</v>
+        <v>14.70491730440479</v>
       </c>
     </row>
     <row r="47">
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>14.90097207929845</v>
+        <v>14.70491730440479</v>
       </c>
     </row>
     <row r="48">
@@ -2409,7 +2409,7 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>14.90097207929845</v>
+        <v>14.9139321578258</v>
       </c>
     </row>
     <row r="49">
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>15.39058793177672</v>
+        <v>15.39818561758153</v>
       </c>
     </row>
     <row r="50">
@@ -2491,7 +2491,7 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>15.55279586015389</v>
+        <v>15.55789316181155</v>
       </c>
     </row>
     <row r="51">
@@ -2532,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>16.46410452789935</v>
+        <v>16.44727977295515</v>
       </c>
     </row>
     <row r="52">
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>17.37544874440357</v>
+        <v>17.34712478394894</v>
       </c>
     </row>
     <row r="53">
@@ -2614,7 +2614,7 @@
         <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>18.99504856873714</v>
+        <v>19.09058139794423</v>
       </c>
     </row>
     <row r="54">
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>19.35440687995326</v>
+        <v>19.36955181416631</v>
       </c>
     </row>
     <row r="55">
@@ -2696,7 +2696,7 @@
         <v>11</v>
       </c>
       <c r="K55" t="n">
-        <v>20.44211148955486</v>
+        <v>20.45962582445294</v>
       </c>
     </row>
     <row r="56">
@@ -2737,7 +2737,7 @@
         <v>11</v>
       </c>
       <c r="K56" t="n">
-        <v>20.85513318717049</v>
+        <v>20.87189659295924</v>
       </c>
     </row>
     <row r="57">
@@ -2778,7 +2778,7 @@
         <v>11</v>
       </c>
       <c r="K57" t="n">
-        <v>21.24417781615288</v>
+        <v>21.25932422424625</v>
       </c>
     </row>
     <row r="58">
@@ -2819,7 +2819,7 @@
         <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>21.57890195439783</v>
+        <v>21.5931175452996</v>
       </c>
     </row>
     <row r="59">
@@ -2860,7 +2860,7 @@
         <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>22.69930894948986</v>
+        <v>22.74831999714625</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +2901,7 @@
         <v>11</v>
       </c>
       <c r="K60" t="n">
-        <v>24.17628142732889</v>
+        <v>24.24128253786889</v>
       </c>
     </row>
     <row r="61">
@@ -2942,7 +2942,7 @@
         <v>11</v>
       </c>
       <c r="K61" t="n">
-        <v>24.17628142732889</v>
+        <v>24.24128253786889</v>
       </c>
     </row>
     <row r="62">
@@ -2983,7 +2983,7 @@
         <v>11</v>
       </c>
       <c r="K62" t="n">
-        <v>24.17628142732889</v>
+        <v>24.24128253786889</v>
       </c>
     </row>
     <row r="63">
@@ -3024,7 +3024,7 @@
         <v>11</v>
       </c>
       <c r="K63" t="n">
-        <v>26.20186131343188</v>
+        <v>26.13980280489467</v>
       </c>
     </row>
     <row r="64">
@@ -3065,7 +3065,7 @@
         <v>11</v>
       </c>
       <c r="K64" t="n">
-        <v>26.20186131343188</v>
+        <v>26.13980280489467</v>
       </c>
     </row>
     <row r="65">
@@ -3106,7 +3106,7 @@
         <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>25.66606308824377</v>
+        <v>26.00010138171323</v>
       </c>
     </row>
     <row r="66">
@@ -3147,7 +3147,7 @@
         <v>11</v>
       </c>
       <c r="K66" t="n">
-        <v>25.66606308824377</v>
+        <v>25.49191108175334</v>
       </c>
     </row>
     <row r="67">
@@ -3188,7 +3188,7 @@
         <v>11</v>
       </c>
       <c r="K67" t="n">
-        <v>25.66606308824377</v>
+        <v>25.49191108175334</v>
       </c>
     </row>
     <row r="68">
@@ -3229,7 +3229,7 @@
         <v>11</v>
       </c>
       <c r="K68" t="n">
-        <v>25.66606308824377</v>
+        <v>25.49191108175334</v>
       </c>
     </row>
     <row r="69">
@@ -3270,7 +3270,7 @@
         <v>11</v>
       </c>
       <c r="K69" t="n">
-        <v>24.51820949168631</v>
+        <v>24.56357073298082</v>
       </c>
     </row>
     <row r="70">
@@ -3311,7 +3311,7 @@
         <v>11</v>
       </c>
       <c r="K70" t="n">
-        <v>24.17916618470565</v>
+        <v>24.2124650153238</v>
       </c>
     </row>
     <row r="71">
@@ -3352,7 +3352,7 @@
         <v>11</v>
       </c>
       <c r="K71" t="n">
-        <v>25.5966815762619</v>
+        <v>25.63387442790525</v>
       </c>
     </row>
     <row r="72">
@@ -3393,7 +3393,7 @@
         <v>11</v>
       </c>
       <c r="K72" t="n">
-        <v>26.88995911838267</v>
+        <v>22.33078238648552</v>
       </c>
     </row>
     <row r="73">
@@ -3434,7 +3434,7 @@
         <v>11</v>
       </c>
       <c r="K73" t="n">
-        <v>26.88995911838267</v>
+        <v>22.33078238648552</v>
       </c>
     </row>
     <row r="74">
@@ -3475,7 +3475,7 @@
         <v>11</v>
       </c>
       <c r="K74" t="n">
-        <v>28.52316172484845</v>
+        <v>28.58911449557269</v>
       </c>
     </row>
     <row r="75">
@@ -3516,7 +3516,7 @@
         <v>11</v>
       </c>
       <c r="K75" t="n">
-        <v>30.66588861137356</v>
+        <v>30.67952774302107</v>
       </c>
     </row>
     <row r="76">
@@ -3557,7 +3557,7 @@
         <v>11</v>
       </c>
       <c r="K76" t="n">
-        <v>30.66588861137356</v>
+        <v>30.67952774302107</v>
       </c>
     </row>
     <row r="77">
@@ -3598,7 +3598,7 @@
         <v>11</v>
       </c>
       <c r="K77" t="n">
-        <v>32.12320473761747</v>
+        <v>32.15530502821533</v>
       </c>
     </row>
     <row r="78">
@@ -3639,7 +3639,7 @@
         <v>11</v>
       </c>
       <c r="K78" t="n">
-        <v>33.20937179433919</v>
+        <v>22.38520659719642</v>
       </c>
     </row>
     <row r="79">
@@ -3680,7 +3680,7 @@
         <v>11</v>
       </c>
       <c r="K79" t="n">
-        <v>29.94731022881903</v>
+        <v>30.0963262515195</v>
       </c>
     </row>
     <row r="80">
@@ -3721,7 +3721,7 @@
         <v>11</v>
       </c>
       <c r="K80" t="n">
-        <v>29.94731022881903</v>
+        <v>30.0963262515195</v>
       </c>
     </row>
     <row r="81">
@@ -3762,7 +3762,7 @@
         <v>11</v>
       </c>
       <c r="K81" t="n">
-        <v>33.25403074862375</v>
+        <v>33.28538885308625</v>
       </c>
     </row>
     <row r="82">
@@ -3803,7 +3803,7 @@
         <v>11</v>
       </c>
       <c r="K82" t="n">
-        <v>35.74430957912962</v>
+        <v>35.18710400624892</v>
       </c>
     </row>
     <row r="83">
@@ -3844,7 +3844,7 @@
         <v>11</v>
       </c>
       <c r="K83" t="n">
-        <v>35.22205046464095</v>
+        <v>35.1831624682064</v>
       </c>
     </row>
     <row r="84">
@@ -3885,7 +3885,7 @@
         <v>11</v>
       </c>
       <c r="K84" t="n">
-        <v>32.3137282444406</v>
+        <v>32.25135624930163</v>
       </c>
     </row>
     <row r="85">
@@ -3926,7 +3926,7 @@
         <v>17</v>
       </c>
       <c r="K85" t="n">
-        <v>3.655625202153288</v>
+        <v>3.642125819453386</v>
       </c>
     </row>
     <row r="86">
@@ -3967,7 +3967,7 @@
         <v>17</v>
       </c>
       <c r="K86" t="n">
-        <v>3.264927063259222</v>
+        <v>3.255358354232785</v>
       </c>
     </row>
     <row r="87">
@@ -4008,7 +4008,7 @@
         <v>17</v>
       </c>
       <c r="K87" t="n">
-        <v>2.399377731464309</v>
+        <v>2.398105996301588</v>
       </c>
     </row>
     <row r="88">
@@ -4049,7 +4049,7 @@
         <v>17</v>
       </c>
       <c r="K88" t="n">
-        <v>2.355884347339752</v>
+        <v>2.354719534730244</v>
       </c>
     </row>
     <row r="89">
@@ -4090,7 +4090,7 @@
         <v>17</v>
       </c>
       <c r="K89" t="n">
-        <v>2.252836045045917</v>
+        <v>2.251765918996991</v>
       </c>
     </row>
     <row r="90">
@@ -4131,7 +4131,7 @@
         <v>17</v>
       </c>
       <c r="K90" t="n">
-        <v>2.21979661522538</v>
+        <v>2.218923888940998</v>
       </c>
     </row>
     <row r="91">
@@ -4172,7 +4172,7 @@
         <v>17</v>
       </c>
       <c r="K91" t="n">
-        <v>2.252146836654987</v>
+        <v>2.253347188363659</v>
       </c>
     </row>
     <row r="92">
@@ -4213,7 +4213,7 @@
         <v>17</v>
       </c>
       <c r="K92" t="n">
-        <v>2.30019580561668</v>
+        <v>2.301226502659204</v>
       </c>
     </row>
     <row r="93">
@@ -4254,7 +4254,7 @@
         <v>17</v>
       </c>
       <c r="K93" t="n">
-        <v>2.352384292151674</v>
+        <v>2.301226502659204</v>
       </c>
     </row>
     <row r="94">
@@ -4295,7 +4295,7 @@
         <v>17</v>
       </c>
       <c r="K94" t="n">
-        <v>2.352384292151674</v>
+        <v>2.301226502659204</v>
       </c>
     </row>
     <row r="95">
@@ -4336,7 +4336,7 @@
         <v>17</v>
       </c>
       <c r="K95" t="n">
-        <v>2.550873196243217</v>
+        <v>2.489734249269353</v>
       </c>
     </row>
     <row r="96">
@@ -4377,7 +4377,7 @@
         <v>17</v>
       </c>
       <c r="K96" t="n">
-        <v>2.550873196243217</v>
+        <v>2.553315915595588</v>
       </c>
     </row>
     <row r="97">
@@ -4418,7 +4418,7 @@
         <v>17</v>
       </c>
       <c r="K97" t="n">
-        <v>2.550873196243217</v>
+        <v>2.553315915595588</v>
       </c>
     </row>
     <row r="98">
@@ -4459,7 +4459,7 @@
         <v>17</v>
       </c>
       <c r="K98" t="n">
-        <v>2.550873196243217</v>
+        <v>2.553315915595588</v>
       </c>
     </row>
     <row r="99">
@@ -4500,7 +4500,7 @@
         <v>17</v>
       </c>
       <c r="K99" t="n">
-        <v>2.653203568705818</v>
+        <v>2.655054926060676</v>
       </c>
     </row>
     <row r="100">
@@ -4541,7 +4541,7 @@
         <v>17</v>
       </c>
       <c r="K100" t="n">
-        <v>2.643804707830325</v>
+        <v>2.643513293066809</v>
       </c>
     </row>
     <row r="101">
@@ -4582,7 +4582,7 @@
         <v>17</v>
       </c>
       <c r="K101" t="n">
-        <v>2.418092743267994</v>
+        <v>2.518260643654614</v>
       </c>
     </row>
     <row r="102">
@@ -4623,7 +4623,7 @@
         <v>17</v>
       </c>
       <c r="K102" t="n">
-        <v>2.342415712804469</v>
+        <v>2.340871106880618</v>
       </c>
     </row>
     <row r="103">
@@ -4664,7 +4664,7 @@
         <v>17</v>
       </c>
       <c r="K103" t="n">
-        <v>2.342415712804469</v>
+        <v>2.340871106880618</v>
       </c>
     </row>
     <row r="104">
@@ -4705,7 +4705,7 @@
         <v>17</v>
       </c>
       <c r="K104" t="n">
-        <v>2.268576143173112</v>
+        <v>2.267182618065173</v>
       </c>
     </row>
     <row r="105">
@@ -4746,7 +4746,7 @@
         <v>17</v>
       </c>
       <c r="K105" t="n">
-        <v>2.268576143173112</v>
+        <v>2.267182618065173</v>
       </c>
     </row>
     <row r="106">
@@ -4787,7 +4787,7 @@
         <v>17</v>
       </c>
       <c r="K106" t="n">
-        <v>2.217132450735882</v>
+        <v>2.216829882042773</v>
       </c>
     </row>
     <row r="107">
@@ -4828,7 +4828,7 @@
         <v>17</v>
       </c>
       <c r="K107" t="n">
-        <v>2.2116895385719</v>
+        <v>2.211854409627325</v>
       </c>
     </row>
     <row r="108">
@@ -4869,7 +4869,7 @@
         <v>17</v>
       </c>
       <c r="K108" t="n">
-        <v>2.205518959400552</v>
+        <v>2.204903626958802</v>
       </c>
     </row>
     <row r="109">
@@ -4910,7 +4910,7 @@
         <v>17</v>
       </c>
       <c r="K109" t="n">
-        <v>2.185617419654481</v>
+        <v>2.184586328633258</v>
       </c>
     </row>
     <row r="110">
@@ -4951,7 +4951,7 @@
         <v>17</v>
       </c>
       <c r="K110" t="n">
-        <v>2.155007908898329</v>
+        <v>2.153742406572132</v>
       </c>
     </row>
     <row r="111">
@@ -4992,7 +4992,7 @@
         <v>17</v>
       </c>
       <c r="K111" t="n">
-        <v>2.121820681858065</v>
+        <v>2.122383846363779</v>
       </c>
     </row>
     <row r="112">
@@ -5033,7 +5033,7 @@
         <v>17</v>
       </c>
       <c r="K112" t="n">
-        <v>2.121820681858065</v>
+        <v>2.122383846363779</v>
       </c>
     </row>
     <row r="113">
@@ -5074,7 +5074,7 @@
         <v>17</v>
       </c>
       <c r="K113" t="n">
-        <v>2.249804039781183</v>
+        <v>2.251000276695078</v>
       </c>
     </row>
     <row r="114">
@@ -5115,7 +5115,7 @@
         <v>17</v>
       </c>
       <c r="K114" t="n">
-        <v>2.276935456485526</v>
+        <v>2.277673647184799</v>
       </c>
     </row>
     <row r="115">
@@ -5156,7 +5156,7 @@
         <v>17</v>
       </c>
       <c r="K115" t="n">
-        <v>2.294309311820022</v>
+        <v>2.294750488747078</v>
       </c>
     </row>
     <row r="116">
@@ -5197,7 +5197,7 @@
         <v>17</v>
       </c>
       <c r="K116" t="n">
-        <v>2.313323918834337</v>
+        <v>2.313867334222721</v>
       </c>
     </row>
     <row r="117">
@@ -5238,7 +5238,7 @@
         <v>17</v>
       </c>
       <c r="K117" t="n">
-        <v>2.313323918834337</v>
+        <v>2.313867334222721</v>
       </c>
     </row>
     <row r="118">
@@ -5279,7 +5279,7 @@
         <v>17</v>
       </c>
       <c r="K118" t="n">
-        <v>2.319676220724453</v>
+        <v>2.319466391467313</v>
       </c>
     </row>
     <row r="119">
@@ -5320,7 +5320,7 @@
         <v>17</v>
       </c>
       <c r="K119" t="n">
-        <v>2.282193623509603</v>
+        <v>2.281309496953031</v>
       </c>
     </row>
     <row r="120">
@@ -5361,7 +5361,7 @@
         <v>17</v>
       </c>
       <c r="K120" t="n">
-        <v>2.261802382317713</v>
+        <v>2.26132578279934</v>
       </c>
     </row>
     <row r="121">
@@ -5402,7 +5402,7 @@
         <v>17</v>
       </c>
       <c r="K121" t="n">
-        <v>2.255876719294342</v>
+        <v>2.255852802350268</v>
       </c>
     </row>
     <row r="122">
@@ -5443,7 +5443,7 @@
         <v>17</v>
       </c>
       <c r="K122" t="n">
-        <v>2.255876719294342</v>
+        <v>2.255852802350268</v>
       </c>
     </row>
     <row r="123">
@@ -5484,7 +5484,7 @@
         <v>17</v>
       </c>
       <c r="K123" t="n">
-        <v>2.278145012965538</v>
+        <v>2.278718840385056</v>
       </c>
     </row>
     <row r="124">
@@ -5525,7 +5525,7 @@
         <v>17</v>
       </c>
       <c r="K124" t="n">
-        <v>2.278145012965538</v>
+        <v>2.278718840385056</v>
       </c>
     </row>
     <row r="125">
@@ -5566,7 +5566,7 @@
         <v>17</v>
       </c>
       <c r="K125" t="n">
-        <v>2.29998581674779</v>
+        <v>2.300988819494015</v>
       </c>
     </row>
     <row r="126">
@@ -5607,7 +5607,7 @@
         <v>17</v>
       </c>
       <c r="K126" t="n">
-        <v>2.39899655611404</v>
+        <v>2.400491992516112</v>
       </c>
     </row>
     <row r="127">
@@ -5648,7 +5648,7 @@
         <v>17</v>
       </c>
       <c r="K127" t="n">
-        <v>2.426003596047259</v>
+        <v>2.426433234651199</v>
       </c>
     </row>
     <row r="128">
@@ -5689,7 +5689,7 @@
         <v>17</v>
       </c>
       <c r="K128" t="n">
-        <v>2.43304178777875</v>
+        <v>2.433166299696604</v>
       </c>
     </row>
     <row r="129">
@@ -5730,7 +5730,7 @@
         <v>17</v>
       </c>
       <c r="K129" t="n">
-        <v>2.329533845651123</v>
+        <v>2.328854369026954</v>
       </c>
     </row>
     <row r="130">
@@ -5771,7 +5771,7 @@
         <v>17</v>
       </c>
       <c r="K130" t="n">
-        <v>2.329533845651123</v>
+        <v>2.328854369026954</v>
       </c>
     </row>
     <row r="131">
@@ -5812,7 +5812,7 @@
         <v>17</v>
       </c>
       <c r="K131" t="n">
-        <v>2.329533845651123</v>
+        <v>2.328854369026954</v>
       </c>
     </row>
     <row r="132">
@@ -5853,7 +5853,7 @@
         <v>17</v>
       </c>
       <c r="K132" t="n">
-        <v>2.275503708438266</v>
+        <v>2.273868442889747</v>
       </c>
     </row>
     <row r="133">
@@ -5894,7 +5894,7 @@
         <v>17</v>
       </c>
       <c r="K133" t="n">
-        <v>2.129964220088542</v>
+        <v>2.128291034343583</v>
       </c>
     </row>
     <row r="134">
@@ -5935,7 +5935,7 @@
         <v>17</v>
       </c>
       <c r="K134" t="n">
-        <v>1.726676601806959</v>
+        <v>1.720801904835842</v>
       </c>
     </row>
     <row r="135">
@@ -5976,7 +5976,7 @@
         <v>17</v>
       </c>
       <c r="K135" t="n">
-        <v>1.726676601806959</v>
+        <v>1.720801904835842</v>
       </c>
     </row>
     <row r="136">
@@ -6017,7 +6017,7 @@
         <v>17</v>
       </c>
       <c r="K136" t="n">
-        <v>1.604021776767994</v>
+        <v>1.598275715985946</v>
       </c>
     </row>
     <row r="137">
@@ -6058,7 +6058,7 @@
         <v>17</v>
       </c>
       <c r="K137" t="n">
-        <v>1.495663010984039</v>
+        <v>1.491482234915091</v>
       </c>
     </row>
     <row r="138">
@@ -6099,7 +6099,7 @@
         <v>17</v>
       </c>
       <c r="K138" t="n">
-        <v>1.495663010984039</v>
+        <v>1.491482234915091</v>
       </c>
     </row>
     <row r="139">
@@ -6140,7 +6140,7 @@
         <v>17</v>
       </c>
       <c r="K139" t="n">
-        <v>1.140911278710099</v>
+        <v>1.134665013898365</v>
       </c>
     </row>
     <row r="140">
@@ -6181,7 +6181,7 @@
         <v>17</v>
       </c>
       <c r="K140" t="n">
-        <v>0.9804261502569596</v>
+        <v>0.9788732688213817</v>
       </c>
     </row>
     <row r="141">
@@ -6222,7 +6222,7 @@
         <v>17</v>
       </c>
       <c r="K141" t="n">
-        <v>0.947668382193923</v>
+        <v>0.9478262599968733</v>
       </c>
     </row>
     <row r="142">
@@ -6263,7 +6263,7 @@
         <v>17</v>
       </c>
       <c r="K142" t="n">
-        <v>1.046449695602111</v>
+        <v>1.047773289556459</v>
       </c>
     </row>
     <row r="143">
@@ -6304,7 +6304,7 @@
         <v>17</v>
       </c>
       <c r="K143" t="n">
-        <v>1.046449695602111</v>
+        <v>1.047773289556459</v>
       </c>
     </row>
     <row r="144">
@@ -6345,7 +6345,7 @@
         <v>17</v>
       </c>
       <c r="K144" t="n">
-        <v>1.094491209829949</v>
+        <v>1.095635378655122</v>
       </c>
     </row>
     <row r="145">
@@ -6386,7 +6386,7 @@
         <v>17</v>
       </c>
       <c r="K145" t="n">
-        <v>1.121456763951091</v>
+        <v>1.12276815977813</v>
       </c>
     </row>
     <row r="146">
@@ -6427,7 +6427,7 @@
         <v>17</v>
       </c>
       <c r="K146" t="n">
-        <v>1.160223779553904</v>
+        <v>1.162272388056961</v>
       </c>
     </row>
     <row r="147">
@@ -6468,7 +6468,7 @@
         <v>17</v>
       </c>
       <c r="K147" t="n">
-        <v>1.427812544501824</v>
+        <v>1.430509800817653</v>
       </c>
     </row>
     <row r="148">
@@ -6509,7 +6509,7 @@
         <v>17</v>
       </c>
       <c r="K148" t="n">
-        <v>1.427812544501824</v>
+        <v>1.430509800817653</v>
       </c>
     </row>
     <row r="149">
@@ -6550,7 +6550,7 @@
         <v>17</v>
       </c>
       <c r="K149" t="n">
-        <v>1.755441115818343</v>
+        <v>1.757496593321768</v>
       </c>
     </row>
     <row r="150">
@@ -6591,7 +6591,7 @@
         <v>17</v>
       </c>
       <c r="K150" t="n">
-        <v>1.755441115818343</v>
+        <v>1.757496593321768</v>
       </c>
     </row>
     <row r="151">
@@ -6632,7 +6632,7 @@
         <v>17</v>
       </c>
       <c r="K151" t="n">
-        <v>1.788673379144996</v>
+        <v>1.789005990939995</v>
       </c>
     </row>
     <row r="152">
@@ -6673,7 +6673,7 @@
         <v>17</v>
       </c>
       <c r="K152" t="n">
-        <v>1.778274352829337</v>
+        <v>1.778211637127946</v>
       </c>
     </row>
     <row r="153">
@@ -6714,7 +6714,7 @@
         <v>17</v>
       </c>
       <c r="K153" t="n">
-        <v>1.778274352829337</v>
+        <v>1.778211637127946</v>
       </c>
     </row>
     <row r="154">
@@ -6755,7 +6755,7 @@
         <v>17</v>
       </c>
       <c r="K154" t="n">
-        <v>1.772817011596296</v>
+        <v>1.77206441721475</v>
       </c>
     </row>
     <row r="155">
@@ -6796,7 +6796,7 @@
         <v>17</v>
       </c>
       <c r="K155" t="n">
-        <v>1.752865128020558</v>
+        <v>1.751891028671269</v>
       </c>
     </row>
     <row r="156">
@@ -6837,7 +6837,7 @@
         <v>17</v>
       </c>
       <c r="K156" t="n">
-        <v>1.701855296213878</v>
+        <v>1.69915042491716</v>
       </c>
     </row>
     <row r="157">
@@ -6878,7 +6878,7 @@
         <v>17</v>
       </c>
       <c r="K157" t="n">
-        <v>1.39792805562581</v>
+        <v>1.395470510692885</v>
       </c>
     </row>
     <row r="158">
@@ -6919,7 +6919,7 @@
         <v>17</v>
       </c>
       <c r="K158" t="n">
-        <v>1.39792805562581</v>
+        <v>1.395470510692885</v>
       </c>
     </row>
     <row r="159">
@@ -6960,7 +6960,7 @@
         <v>17</v>
       </c>
       <c r="K159" t="n">
-        <v>1.327320467937538</v>
+        <v>1.324849022762463</v>
       </c>
     </row>
     <row r="160">
@@ -7001,7 +7001,7 @@
         <v>17</v>
       </c>
       <c r="K160" t="n">
-        <v>1.1971891976014</v>
+        <v>1.195349386467163</v>
       </c>
     </row>
     <row r="161">
@@ -7042,7 +7042,7 @@
         <v>17</v>
       </c>
       <c r="K161" t="n">
-        <v>1.1971891976014</v>
+        <v>1.195349386467163</v>
       </c>
     </row>
     <row r="162">
@@ -7083,7 +7083,7 @@
         <v>17</v>
       </c>
       <c r="K162" t="n">
-        <v>1.1971891976014</v>
+        <v>1.195349386467163</v>
       </c>
     </row>
     <row r="163">
@@ -7124,7 +7124,7 @@
         <v>17</v>
       </c>
       <c r="K163" t="n">
-        <v>1.144755081883404</v>
+        <v>1.143138415192682</v>
       </c>
     </row>
     <row r="164">
@@ -7165,7 +7165,7 @@
         <v>17</v>
       </c>
       <c r="K164" t="n">
-        <v>1.110326020176739</v>
+        <v>1.109699562533763</v>
       </c>
     </row>
     <row r="165">
@@ -7206,7 +7206,7 @@
         <v>17</v>
       </c>
       <c r="K165" t="n">
-        <v>1.127592304758405</v>
+        <v>1.127925107555623</v>
       </c>
     </row>
     <row r="166">
@@ -7247,7 +7247,7 @@
         <v>17</v>
       </c>
       <c r="K166" t="n">
-        <v>1.129235734728124</v>
+        <v>1.128999637704991</v>
       </c>
     </row>
     <row r="167">
@@ -7288,7 +7288,7 @@
         <v>17</v>
       </c>
       <c r="K167" t="n">
-        <v>1.129235734728124</v>
+        <v>1.128999637704991</v>
       </c>
     </row>
     <row r="168">
@@ -7329,7 +7329,7 @@
         <v>17</v>
       </c>
       <c r="K168" t="n">
-        <v>1.129235734728124</v>
+        <v>1.128999637704991</v>
       </c>
     </row>
     <row r="169">
@@ -7370,7 +7370,7 @@
         <v>17</v>
       </c>
       <c r="K169" t="n">
-        <v>1.07931209195279</v>
+        <v>1.078132302319271</v>
       </c>
     </row>
     <row r="170">
@@ -7411,7 +7411,7 @@
         <v>17</v>
       </c>
       <c r="K170" t="n">
-        <v>1.007523819185527</v>
+        <v>1.006580384496336</v>
       </c>
     </row>
     <row r="171">
@@ -7452,7 +7452,7 @@
         <v>17</v>
       </c>
       <c r="K171" t="n">
-        <v>0.9898694112683336</v>
+        <v>0.9899388197681704</v>
       </c>
     </row>
     <row r="172">
@@ -7493,7 +7493,7 @@
         <v>17</v>
       </c>
       <c r="K172" t="n">
-        <v>0.9914543051707039</v>
+        <v>0.9914318695966965</v>
       </c>
     </row>
     <row r="173">
@@ -7534,7 +7534,7 @@
         <v>17</v>
       </c>
       <c r="K173" t="n">
-        <v>0.9914543051707039</v>
+        <v>0.9914318695966965</v>
       </c>
     </row>
     <row r="174">
@@ -7575,7 +7575,7 @@
         <v>17</v>
       </c>
       <c r="K174" t="n">
-        <v>1.06923049452409</v>
+        <v>1.070830314670122</v>
       </c>
     </row>
     <row r="175">
@@ -7616,7 +7616,7 @@
         <v>17</v>
       </c>
       <c r="K175" t="n">
-        <v>1.187175472566269</v>
+        <v>1.189002425173676</v>
       </c>
     </row>
     <row r="176">
@@ -7657,7 +7657,7 @@
         <v>17</v>
       </c>
       <c r="K176" t="n">
-        <v>1.333556077280552</v>
+        <v>1.333565658438912</v>
       </c>
     </row>
     <row r="177">
@@ -7698,7 +7698,7 @@
         <v>17</v>
       </c>
       <c r="K177" t="n">
-        <v>1.312922373703677</v>
+        <v>1.311819253749365</v>
       </c>
     </row>
     <row r="178">
@@ -7739,7 +7739,7 @@
         <v>17</v>
       </c>
       <c r="K178" t="n">
-        <v>1.269293198848958</v>
+        <v>1.26813063008406</v>
       </c>
     </row>
     <row r="179">
@@ -7780,7 +7780,7 @@
         <v>17</v>
       </c>
       <c r="K179" t="n">
-        <v>1.269293198848958</v>
+        <v>1.26813063008406</v>
       </c>
     </row>
     <row r="180">
@@ -7821,7 +7821,7 @@
         <v>17</v>
       </c>
       <c r="K180" t="n">
-        <v>1.167607646918589</v>
+        <v>1.167201635602541</v>
       </c>
     </row>
     <row r="181">
@@ -7862,7 +7862,7 @@
         <v>17</v>
       </c>
       <c r="K181" t="n">
-        <v>1.058335978988722</v>
+        <v>1.057776064385731</v>
       </c>
     </row>
     <row r="182">
@@ -7903,7 +7903,7 @@
         <v>17</v>
       </c>
       <c r="K182" t="n">
-        <v>1.072186129913543</v>
+        <v>1.072418604357054</v>
       </c>
     </row>
     <row r="183">
@@ -7944,7 +7944,7 @@
         <v>17</v>
       </c>
       <c r="K183" t="n">
-        <v>1.104115376478233</v>
+        <v>1.104810542344077</v>
       </c>
     </row>
     <row r="184">
@@ -7985,7 +7985,7 @@
         <v>17</v>
       </c>
       <c r="K184" t="n">
-        <v>1.141062351849522</v>
+        <v>1.141152858016309</v>
       </c>
     </row>
     <row r="185">
@@ -8026,7 +8026,7 @@
         <v>17</v>
       </c>
       <c r="K185" t="n">
-        <v>1.191043762367248</v>
+        <v>1.192255315039814</v>
       </c>
     </row>
     <row r="186">
@@ -8067,7 +8067,7 @@
         <v>17</v>
       </c>
       <c r="K186" t="n">
-        <v>1.191043762367248</v>
+        <v>1.192255315039814</v>
       </c>
     </row>
     <row r="187">
@@ -8108,7 +8108,7 @@
         <v>17</v>
       </c>
       <c r="K187" t="n">
-        <v>1.486028554703088</v>
+        <v>1.487461797283134</v>
       </c>
     </row>
     <row r="188">
@@ -8149,7 +8149,7 @@
         <v>17</v>
       </c>
       <c r="K188" t="n">
-        <v>1.547807787268301</v>
+        <v>1.548748605141129</v>
       </c>
     </row>
     <row r="189">
@@ -8190,7 +8190,7 @@
         <v>17</v>
       </c>
       <c r="K189" t="n">
-        <v>1.844475967958824</v>
+        <v>1.844802313212991</v>
       </c>
     </row>
     <row r="190">
@@ -8231,7 +8231,7 @@
         <v>17</v>
       </c>
       <c r="K190" t="n">
-        <v>1.841571538570617</v>
+        <v>1.84114621481359</v>
       </c>
     </row>
     <row r="191">
@@ -8272,7 +8272,7 @@
         <v>17</v>
       </c>
       <c r="K191" t="n">
-        <v>1.841571538570617</v>
+        <v>1.84114621481359</v>
       </c>
     </row>
     <row r="192">
@@ -8313,7 +8313,7 @@
         <v>17</v>
       </c>
       <c r="K192" t="n">
-        <v>1.720576971928573</v>
+        <v>1.719355082918982</v>
       </c>
     </row>
     <row r="193">
@@ -8354,7 +8354,7 @@
         <v>17</v>
       </c>
       <c r="K193" t="n">
-        <v>1.643774409243683</v>
+        <v>1.642536369273613</v>
       </c>
     </row>
     <row r="194">
@@ -8395,7 +8395,7 @@
         <v>17</v>
       </c>
       <c r="K194" t="n">
-        <v>1.643774409243683</v>
+        <v>1.642536369273613</v>
       </c>
     </row>
     <row r="195">
@@ -8436,7 +8436,7 @@
         <v>17</v>
       </c>
       <c r="K195" t="n">
-        <v>1.555805184715616</v>
+        <v>1.554274485292735</v>
       </c>
     </row>
     <row r="196">
@@ -8477,7 +8477,7 @@
         <v>17</v>
       </c>
       <c r="K196" t="n">
-        <v>1.278466120075154</v>
+        <v>1.277410331539602</v>
       </c>
     </row>
     <row r="197">
@@ -8518,7 +8518,7 @@
         <v>17</v>
       </c>
       <c r="K197" t="n">
-        <v>1.200149342274758</v>
+        <v>1.19907899481458</v>
       </c>
     </row>
     <row r="198">
@@ -8559,7 +8559,7 @@
         <v>17</v>
       </c>
       <c r="K198" t="n">
-        <v>0.8658938311966332</v>
+        <v>0.8651156562453568</v>
       </c>
     </row>
     <row r="199">
@@ -8600,7 +8600,7 @@
         <v>17</v>
       </c>
       <c r="K199" t="n">
-        <v>0.8658938311966332</v>
+        <v>0.8651156562453568</v>
       </c>
     </row>
     <row r="200">
@@ -8641,7 +8641,7 @@
         <v>17</v>
       </c>
       <c r="K200" t="n">
-        <v>0.8658938311966332</v>
+        <v>0.8651156562453568</v>
       </c>
     </row>
     <row r="201">
@@ -8682,7 +8682,7 @@
         <v>17</v>
       </c>
       <c r="K201" t="n">
-        <v>0.7954039355764896</v>
+        <v>0.7945090211968119</v>
       </c>
     </row>
     <row r="202">
@@ -8723,7 +8723,7 @@
         <v>17</v>
       </c>
       <c r="K202" t="n">
-        <v>0.6192300669665526</v>
+        <v>0.6183973554889365</v>
       </c>
     </row>
     <row r="203">
@@ -8764,7 +8764,7 @@
         <v>17</v>
       </c>
       <c r="K203" t="n">
-        <v>0.5385163421711662</v>
+        <v>0.5382015538476752</v>
       </c>
     </row>
     <row r="204">
@@ -8805,7 +8805,7 @@
         <v>17</v>
       </c>
       <c r="K204" t="n">
-        <v>0.4522874703617749</v>
+        <v>0.4521278570745698</v>
       </c>
     </row>
     <row r="205">
@@ -8846,7 +8846,7 @@
         <v>17</v>
       </c>
       <c r="K205" t="n">
-        <v>0.4322579786603727</v>
+        <v>0.4321198345973218</v>
       </c>
     </row>
     <row r="206">
@@ -8887,7 +8887,7 @@
         <v>17</v>
       </c>
       <c r="K206" t="n">
-        <v>0.4041573121506322</v>
+        <v>0.4038849076641726</v>
       </c>
     </row>
     <row r="207">
@@ -8928,7 +8928,7 @@
         <v>17</v>
       </c>
       <c r="K207" t="n">
-        <v>0.4213399913646258</v>
+        <v>0.4218699525635712</v>
       </c>
     </row>
     <row r="208">
@@ -8969,7 +8969,7 @@
         <v>17</v>
       </c>
       <c r="K208" t="n">
-        <v>0.470025857502466</v>
+        <v>0.4707722187943567</v>
       </c>
     </row>
     <row r="209">
@@ -9010,7 +9010,7 @@
         <v>17</v>
       </c>
       <c r="K209" t="n">
-        <v>0.6684152252175423</v>
+        <v>0.6714789403316066</v>
       </c>
     </row>
     <row r="210">
@@ -9051,7 +9051,7 @@
         <v>17</v>
       </c>
       <c r="K210" t="n">
-        <v>0.7179541259534254</v>
+        <v>0.7188562559589849</v>
       </c>
     </row>
     <row r="211">
@@ -9092,7 +9092,7 @@
         <v>17</v>
       </c>
       <c r="K211" t="n">
-        <v>0.7179541259534254</v>
+        <v>0.7188562559589849</v>
       </c>
     </row>
     <row r="212">
@@ -9133,7 +9133,7 @@
         <v>17</v>
       </c>
       <c r="K212" t="n">
-        <v>0.7179541259534254</v>
+        <v>0.7188562559589849</v>
       </c>
     </row>
     <row r="213">
@@ -9174,7 +9174,7 @@
         <v>17</v>
       </c>
       <c r="K213" t="n">
-        <v>0.8504789130187842</v>
+        <v>0.8532998520857752</v>
       </c>
     </row>
     <row r="214">
@@ -9215,7 +9215,7 @@
         <v>17</v>
       </c>
       <c r="K214" t="n">
-        <v>0.8504789130187842</v>
+        <v>0.8532998520857752</v>
       </c>
     </row>
     <row r="215">
@@ -9256,7 +9256,7 @@
         <v>17</v>
       </c>
       <c r="K215" t="n">
-        <v>0.902790715459413</v>
+        <v>0.9040520603033265</v>
       </c>
     </row>
     <row r="216">
@@ -9297,7 +9297,7 @@
         <v>17</v>
       </c>
       <c r="K216" t="n">
-        <v>0.902790715459413</v>
+        <v>0.9040520603033265</v>
       </c>
     </row>
     <row r="217">
@@ -9338,7 +9338,7 @@
         <v>17</v>
       </c>
       <c r="K217" t="n">
-        <v>0.9315183779958096</v>
+        <v>0.9314095588432793</v>
       </c>
     </row>
     <row r="218">
@@ -9379,7 +9379,7 @@
         <v>17</v>
       </c>
       <c r="K218" t="n">
-        <v>0.9315183779958096</v>
+        <v>0.9314095588432793</v>
       </c>
     </row>
     <row r="219">
@@ -9420,7 +9420,7 @@
         <v>17</v>
       </c>
       <c r="K219" t="n">
-        <v>0.8851152668858296</v>
+        <v>0.8844864169514772</v>
       </c>
     </row>
     <row r="220">
@@ -9461,7 +9461,7 @@
         <v>17</v>
       </c>
       <c r="K220" t="n">
-        <v>0.8426817177160192</v>
+        <v>0.8418695730956948</v>
       </c>
     </row>
     <row r="221">
@@ -9502,7 +9502,7 @@
         <v>17</v>
       </c>
       <c r="K221" t="n">
-        <v>0.6938713116664846</v>
+        <v>0.6930677684189502</v>
       </c>
     </row>
     <row r="222">
@@ -9543,7 +9543,7 @@
         <v>17</v>
       </c>
       <c r="K222" t="n">
-        <v>0.6938713116664846</v>
+        <v>0.6930677684189502</v>
       </c>
     </row>
     <row r="223">
@@ -9584,7 +9584,7 @@
         <v>17</v>
       </c>
       <c r="K223" t="n">
-        <v>0.5629841550136426</v>
+        <v>0.5626663577650524</v>
       </c>
     </row>
     <row r="224">
@@ -9625,7 +9625,7 @@
         <v>17</v>
       </c>
       <c r="K224" t="n">
-        <v>0.5463302263033294</v>
+        <v>0.5461080070969886</v>
       </c>
     </row>
     <row r="225">
@@ -9666,7 +9666,7 @@
         <v>17</v>
       </c>
       <c r="K225" t="n">
-        <v>0.5389585101632535</v>
+        <v>0.5391736064784913</v>
       </c>
     </row>
     <row r="226">
@@ -9707,7 +9707,7 @@
         <v>17</v>
       </c>
       <c r="K226" t="n">
-        <v>0.552547338455138</v>
+        <v>0.5528163966377017</v>
       </c>
     </row>
     <row r="227">
@@ -9748,7 +9748,7 @@
         <v>17</v>
       </c>
       <c r="K227" t="n">
-        <v>0.6865475192796013</v>
+        <v>0.6869367356473498</v>
       </c>
     </row>
     <row r="228">
@@ -9789,7 +9789,7 @@
         <v>17</v>
       </c>
       <c r="K228" t="n">
-        <v>0.7107101364517812</v>
+        <v>0.7109010806737983</v>
       </c>
     </row>
     <row r="229">
@@ -9830,7 +9830,7 @@
         <v>17</v>
       </c>
       <c r="K229" t="n">
-        <v>0.6353390966846304</v>
+        <v>0.6350334582411984</v>
       </c>
     </row>
     <row r="230">
@@ -9871,7 +9871,7 @@
         <v>17</v>
       </c>
       <c r="K230" t="n">
-        <v>0.6353390966846304</v>
+        <v>0.6350334582411984</v>
       </c>
     </row>
     <row r="231">
@@ -9912,7 +9912,7 @@
         <v>17</v>
       </c>
       <c r="K231" t="n">
-        <v>0.5467863697612891</v>
+        <v>0.5467380705439097</v>
       </c>
     </row>
     <row r="232">
@@ -9953,7 +9953,7 @@
         <v>17</v>
       </c>
       <c r="K232" t="n">
-        <v>0.5467863697612891</v>
+        <v>0.5467380705439097</v>
       </c>
     </row>
     <row r="233">
@@ -9994,7 +9994,7 @@
         <v>17</v>
       </c>
       <c r="K233" t="n">
-        <v>0.5296327060372106</v>
+        <v>0.5295971516601461</v>
       </c>
     </row>
     <row r="234">
@@ -10035,7 +10035,7 @@
         <v>17</v>
       </c>
       <c r="K234" t="n">
-        <v>0.5371389694150598</v>
+        <v>0.5371396317144246</v>
       </c>
     </row>
     <row r="235">
@@ -10076,7 +10076,7 @@
         <v>17</v>
       </c>
       <c r="K235" t="n">
-        <v>0.5292845606250567</v>
+        <v>0.5291850454511349</v>
       </c>
     </row>
     <row r="236">
@@ -10117,7 +10117,7 @@
         <v>17</v>
       </c>
       <c r="K236" t="n">
-        <v>0.4468478738436192</v>
+        <v>0.4466851048168524</v>
       </c>
     </row>
     <row r="237">
@@ -10158,7 +10158,7 @@
         <v>17</v>
       </c>
       <c r="K237" t="n">
-        <v>0.4468478738436192</v>
+        <v>0.4466851048168524</v>
       </c>
     </row>
     <row r="238">
@@ -10199,7 +10199,7 @@
         <v>17</v>
       </c>
       <c r="K238" t="n">
-        <v>0.3239816099842603</v>
+        <v>0.3237822738950355</v>
       </c>
     </row>
     <row r="239">
@@ -10240,7 +10240,7 @@
         <v>17</v>
       </c>
       <c r="K239" t="n">
-        <v>0.2751216794231886</v>
+        <v>0.2749575999425046</v>
       </c>
     </row>
     <row r="240">
@@ -10281,7 +10281,7 @@
         <v>17</v>
       </c>
       <c r="K240" t="n">
-        <v>0.161947049349651</v>
+        <v>0.1619014299351722</v>
       </c>
     </row>
     <row r="241">
@@ -10322,7 +10322,7 @@
         <v>17</v>
       </c>
       <c r="K241" t="n">
-        <v>0.1422140172117248</v>
+        <v>0.142177771387514</v>
       </c>
     </row>
     <row r="242">
@@ -10363,7 +10363,7 @@
         <v>17</v>
       </c>
       <c r="K242" t="n">
-        <v>0.1229816940742976</v>
+        <v>0.1229522451865707</v>
       </c>
     </row>
     <row r="243">
@@ -10404,7 +10404,7 @@
         <v>17</v>
       </c>
       <c r="K243" t="n">
-        <v>0.09075891683619514</v>
+        <v>0.09074520326948515</v>
       </c>
     </row>
     <row r="244">
@@ -10445,7 +10445,7 @@
         <v>17</v>
       </c>
       <c r="K244" t="n">
-        <v>0.06090024786127952</v>
+        <v>0.06089825857870126</v>
       </c>
     </row>
   </sheetData>
